--- a/frocloud.xlsx
+++ b/frocloud.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dsh\fro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\desktop\Obsidian Vaults\新建文件夹\frocloud\frocloud-DIYPCmarket\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" firstSheet="3" activeTab="7"/>
+    <workbookView windowWidth="23040" windowHeight="9060" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="GPU天梯图" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="613">
   <si>
     <t>NVIDIA</t>
   </si>
@@ -1060,12 +1060,6 @@
   </si>
   <si>
     <t>总和</t>
-  </si>
-  <si>
-    <t>较25</t>
-  </si>
-  <si>
-    <t>较月初</t>
   </si>
   <si>
     <t>7月下旬</t>
@@ -3694,9 +3688,6 @@
     <xf numFmtId="0" fontId="44" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3749,6 +3740,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -4038,7 +4032,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="表样式 1" pivot="0" count="1" xr9:uid="{F55C3F19-4761-4D2A-854D-2A0F3B81F961}">
+    <tableStyle name="表样式 1" pivot="0" count="1" xr9:uid="{7A0C9EF3-3222-409A-BE19-643DFE0AAD46}">
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
   </tableStyles>
@@ -5974,11 +5968,11 @@
   <dimension ref="A1:Z125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.9166666666667" style="107" customWidth="1"/>
-    <col min="2" max="2" width="9.88888888888889" style="107" customWidth="1"/>
-    <col min="3" max="3" width="8.88888888888889" style="107" customWidth="1"/>
-    <col min="4" max="4" width="10.0833333333333" style="107" customWidth="1"/>
-    <col min="5" max="5" width="10.25" style="107" customWidth="1"/>
+    <col min="1" max="1" width="16.9166666666667" style="106" customWidth="1"/>
+    <col min="2" max="2" width="9.88888888888889" style="106" customWidth="1"/>
+    <col min="3" max="3" width="8.88888888888889" style="106" customWidth="1"/>
+    <col min="4" max="4" width="10.0833333333333" style="106" customWidth="1"/>
+    <col min="5" max="5" width="10.25" style="106" customWidth="1"/>
     <col min="6" max="6" width="9.51851851851852" style="113" customWidth="1"/>
     <col min="7" max="7" width="5.96296296296296" style="152" customWidth="1"/>
     <col min="8" max="8" width="5.96296296296296" style="153" customWidth="1"/>
@@ -5986,9 +5980,9 @@
     <col min="10" max="11" width="5.96296296296296" style="153" customWidth="1"/>
     <col min="12" max="13" width="6.55555555555556" style="113" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="9.76851851851852" style="113" customWidth="1"/>
-    <col min="15" max="15" width="7.77777777777778" style="107" customWidth="1"/>
-    <col min="16" max="16" width="11.4444444444444" style="107" customWidth="1"/>
-    <col min="17" max="17" width="13.962962962963" style="107" customWidth="1"/>
+    <col min="15" max="15" width="7.77777777777778" style="106" customWidth="1"/>
+    <col min="16" max="16" width="11.4444444444444" style="106" customWidth="1"/>
+    <col min="17" max="17" width="13.962962962963" style="106" customWidth="1"/>
     <col min="18" max="18" width="6.02777777777778" customWidth="1"/>
     <col min="19" max="19" width="6.92592592592593" customWidth="1"/>
   </cols>
@@ -6078,7 +6072,7 @@
       <c r="Z2" s="165"/>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="106" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="166"/>
@@ -6253,7 +6247,7 @@
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="107" t="s">
+      <c r="A11" s="106" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="168"/>
@@ -6270,10 +6264,10 @@
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:26">
-      <c r="A12" s="107"/>
-      <c r="B12" s="107"/>
-      <c r="C12" s="107"/>
-      <c r="D12" s="107"/>
+      <c r="A12" s="106"/>
+      <c r="B12" s="106"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="106"/>
       <c r="E12" s="168"/>
       <c r="F12" s="167"/>
       <c r="G12" s="146">
@@ -6298,8 +6292,8 @@
         <v>28</v>
       </c>
       <c r="O12" s="119"/>
-      <c r="P12" s="107"/>
-      <c r="Q12" s="107"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="106"/>
       <c r="U12" s="3" t="s">
         <v>29</v>
       </c>
@@ -6427,10 +6421,10 @@
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:21">
-      <c r="A18" s="107"/>
-      <c r="B18" s="107"/>
-      <c r="C18" s="107"/>
-      <c r="D18" s="107"/>
+      <c r="A18" s="106"/>
+      <c r="B18" s="106"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="106"/>
       <c r="E18" s="168"/>
       <c r="F18" s="172"/>
       <c r="G18" s="146">
@@ -6455,8 +6449,8 @@
         <v>9070</v>
       </c>
       <c r="O18" s="171"/>
-      <c r="P18" s="107"/>
-      <c r="Q18" s="107"/>
+      <c r="P18" s="106"/>
+      <c r="Q18" s="106"/>
       <c r="U18" s="173" t="s">
         <v>31</v>
       </c>
@@ -6510,7 +6504,7 @@
       <c r="O20" s="171"/>
     </row>
     <row r="21" spans="1:21">
-      <c r="A21" s="107" t="s">
+      <c r="A21" s="106" t="s">
         <v>37</v>
       </c>
       <c r="E21" s="168"/>
@@ -6526,10 +6520,10 @@
       <c r="O21" s="171"/>
     </row>
     <row r="22" customFormat="1" spans="1:21">
-      <c r="A22" s="107"/>
-      <c r="B22" s="107"/>
-      <c r="C22" s="107"/>
-      <c r="D22" s="107"/>
+      <c r="A22" s="106"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="106"/>
       <c r="E22" s="168"/>
       <c r="F22" s="172" t="s">
         <v>38</v>
@@ -6543,13 +6537,13 @@
       <c r="M22" s="113"/>
       <c r="N22" s="170"/>
       <c r="O22" s="171"/>
-      <c r="P22" s="107"/>
-      <c r="Q22" s="107"/>
+      <c r="P22" s="106"/>
+      <c r="Q22" s="106"/>
     </row>
     <row r="23" customFormat="1" spans="1:21">
-      <c r="A23" s="107"/>
-      <c r="B23" s="107"/>
-      <c r="C23" s="107"/>
+      <c r="A23" s="106"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="106"/>
       <c r="D23" s="168" t="s">
         <v>39</v>
       </c>
@@ -6575,8 +6569,8 @@
       <c r="M23" s="113"/>
       <c r="N23" s="170"/>
       <c r="O23" s="171"/>
-      <c r="P23" s="107"/>
-      <c r="Q23" s="107"/>
+      <c r="P23" s="106"/>
+      <c r="Q23" s="106"/>
     </row>
     <row r="24" spans="1:21">
       <c r="D24" s="168"/>
@@ -6705,9 +6699,9 @@
       <c r="P28" s="119"/>
     </row>
     <row r="29" customFormat="1" spans="1:21">
-      <c r="A29" s="107"/>
-      <c r="B29" s="107"/>
-      <c r="C29" s="107"/>
+      <c r="A29" s="106"/>
+      <c r="B29" s="106"/>
+      <c r="C29" s="106"/>
       <c r="D29" s="168">
         <v>3090</v>
       </c>
@@ -6734,12 +6728,12 @@
       <c r="N29" s="170"/>
       <c r="O29" s="171"/>
       <c r="P29" s="119"/>
-      <c r="Q29" s="107"/>
+      <c r="Q29" s="106"/>
     </row>
     <row r="30" customFormat="1" spans="1:21">
-      <c r="A30" s="107"/>
-      <c r="B30" s="107"/>
-      <c r="C30" s="107"/>
+      <c r="A30" s="106"/>
+      <c r="B30" s="106"/>
+      <c r="C30" s="106"/>
       <c r="D30" s="168" t="s">
         <v>44</v>
       </c>
@@ -6766,7 +6760,7 @@
       <c r="N30" s="170"/>
       <c r="O30" s="171"/>
       <c r="P30" s="119"/>
-      <c r="Q30" s="107"/>
+      <c r="Q30" s="106"/>
     </row>
     <row r="31" spans="1:21">
       <c r="D31" s="168"/>
@@ -6821,9 +6815,9 @@
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:18">
-      <c r="A33" s="107"/>
-      <c r="B33" s="107"/>
-      <c r="C33" s="107"/>
+      <c r="A33" s="106"/>
+      <c r="B33" s="106"/>
+      <c r="C33" s="106"/>
       <c r="D33" s="168" t="s">
         <v>47</v>
       </c>
@@ -6850,7 +6844,7 @@
       <c r="N33" s="170"/>
       <c r="O33" s="171"/>
       <c r="P33" s="171"/>
-      <c r="Q33" s="107"/>
+      <c r="Q33" s="106"/>
     </row>
     <row r="34" spans="1:18">
       <c r="D34" s="168"/>
@@ -6879,9 +6873,9 @@
       <c r="P34" s="171"/>
     </row>
     <row r="35" customFormat="1" spans="1:18">
-      <c r="A35" s="107"/>
-      <c r="B35" s="107"/>
-      <c r="C35" s="107"/>
+      <c r="A35" s="106"/>
+      <c r="B35" s="106"/>
+      <c r="C35" s="106"/>
       <c r="D35" s="168">
         <v>3080</v>
       </c>
@@ -6908,7 +6902,7 @@
       <c r="N35" s="170"/>
       <c r="O35" s="171"/>
       <c r="P35" s="171"/>
-      <c r="Q35" s="107"/>
+      <c r="Q35" s="106"/>
     </row>
     <row r="36" spans="1:18">
       <c r="D36" s="168"/>
@@ -6963,7 +6957,7 @@
       <c r="P37" s="171"/>
     </row>
     <row r="38" spans="1:18">
-      <c r="A38" s="107" t="s">
+      <c r="A38" s="106" t="s">
         <v>50</v>
       </c>
       <c r="D38" s="168"/>
@@ -6981,9 +6975,9 @@
       <c r="P38" s="171"/>
     </row>
     <row r="39" customFormat="1" spans="1:18">
-      <c r="A39" s="107"/>
-      <c r="B39" s="107"/>
-      <c r="C39" s="107"/>
+      <c r="A39" s="106"/>
+      <c r="B39" s="106"/>
+      <c r="C39" s="106"/>
       <c r="D39" s="168"/>
       <c r="E39" s="168"/>
       <c r="F39" s="172"/>
@@ -7010,7 +7004,7 @@
       </c>
       <c r="O39" s="171"/>
       <c r="P39" s="171"/>
-      <c r="Q39" s="107"/>
+      <c r="Q39" s="106"/>
     </row>
     <row r="40" spans="1:18">
       <c r="D40" s="168"/>
@@ -7039,11 +7033,11 @@
       <c r="P40" s="171"/>
     </row>
     <row r="41" customFormat="1" spans="1:18">
-      <c r="A41" s="107" t="s">
+      <c r="A41" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="107"/>
-      <c r="C41" s="107"/>
+      <c r="B41" s="106"/>
+      <c r="C41" s="106"/>
       <c r="D41" s="168"/>
       <c r="E41" s="168"/>
       <c r="F41" s="172"/>
@@ -7068,12 +7062,12 @@
       <c r="N41" s="170"/>
       <c r="O41" s="171"/>
       <c r="P41" s="171"/>
-      <c r="Q41" s="107"/>
+      <c r="Q41" s="106"/>
     </row>
     <row r="42" customFormat="1" spans="1:18">
-      <c r="A42" s="107"/>
-      <c r="B42" s="107"/>
-      <c r="C42" s="107"/>
+      <c r="A42" s="106"/>
+      <c r="B42" s="106"/>
+      <c r="C42" s="106"/>
       <c r="D42" s="168"/>
       <c r="E42" s="168"/>
       <c r="F42" s="172" t="s">
@@ -7100,12 +7094,12 @@
       <c r="N42" s="170"/>
       <c r="O42" s="171"/>
       <c r="P42" s="171"/>
-      <c r="Q42" s="107"/>
+      <c r="Q42" s="106"/>
     </row>
     <row r="43" customFormat="1" spans="1:18">
-      <c r="A43" s="107"/>
-      <c r="B43" s="107"/>
-      <c r="C43" s="107"/>
+      <c r="A43" s="106"/>
+      <c r="B43" s="106"/>
+      <c r="C43" s="106"/>
       <c r="D43" s="168"/>
       <c r="E43" s="168"/>
       <c r="F43" s="172" t="s">
@@ -7132,12 +7126,12 @@
       <c r="N43" s="170"/>
       <c r="O43" s="171"/>
       <c r="P43" s="171"/>
-      <c r="Q43" s="107"/>
+      <c r="Q43" s="106"/>
     </row>
     <row r="44" customFormat="1" spans="1:18">
-      <c r="A44" s="107"/>
-      <c r="B44" s="107"/>
-      <c r="C44" s="107"/>
+      <c r="A44" s="106"/>
+      <c r="B44" s="106"/>
+      <c r="C44" s="106"/>
       <c r="D44" s="168"/>
       <c r="E44" s="168"/>
       <c r="F44" s="172"/>
@@ -7164,7 +7158,7 @@
       </c>
       <c r="O44" s="171"/>
       <c r="P44" s="171"/>
-      <c r="Q44" s="107"/>
+      <c r="Q44" s="106"/>
     </row>
     <row r="45" spans="1:18">
       <c r="D45" s="168"/>
@@ -7192,9 +7186,9 @@
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:18">
-      <c r="A46" s="107"/>
-      <c r="B46" s="107"/>
-      <c r="C46" s="107"/>
+      <c r="A46" s="106"/>
+      <c r="B46" s="106"/>
+      <c r="C46" s="106"/>
       <c r="D46" s="168" t="s">
         <v>57</v>
       </c>
@@ -7221,12 +7215,12 @@
       <c r="N46" s="113"/>
       <c r="O46" s="171"/>
       <c r="P46" s="171"/>
-      <c r="Q46" s="107"/>
+      <c r="Q46" s="106"/>
       <c r="R46" s="4"/>
     </row>
     <row r="47" customFormat="1" spans="1:18">
-      <c r="A47" s="107"/>
-      <c r="B47" s="107"/>
+      <c r="A47" s="106"/>
+      <c r="B47" s="106"/>
       <c r="C47" s="168" t="s">
         <v>58</v>
       </c>
@@ -7254,7 +7248,7 @@
       <c r="N47" s="113"/>
       <c r="O47" s="171"/>
       <c r="P47" s="171"/>
-      <c r="Q47" s="107"/>
+      <c r="Q47" s="106"/>
       <c r="R47" s="4"/>
     </row>
     <row r="48" spans="1:18">
@@ -7285,7 +7279,7 @@
       </c>
     </row>
     <row r="49" spans="1:19">
-      <c r="A49" s="107" t="s">
+      <c r="A49" s="106" t="s">
         <v>60</v>
       </c>
       <c r="C49" s="168"/>
@@ -7331,7 +7325,7 @@
       <c r="R50" s="89"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="107">
+      <c r="A51" s="106">
         <v>6000</v>
       </c>
       <c r="C51" s="168"/>
@@ -7377,8 +7371,8 @@
       <c r="R52" s="89"/>
     </row>
     <row r="53" customFormat="1" spans="1:19">
-      <c r="A53" s="107"/>
-      <c r="B53" s="107"/>
+      <c r="A53" s="106"/>
+      <c r="B53" s="106"/>
       <c r="C53" s="168"/>
       <c r="D53" s="168"/>
       <c r="E53" s="168" t="s">
@@ -7406,13 +7400,13 @@
       <c r="N53" s="113"/>
       <c r="O53" s="171"/>
       <c r="P53" s="171"/>
-      <c r="Q53" s="107"/>
+      <c r="Q53" s="106"/>
       <c r="R53" s="89"/>
       <c r="S53" s="4"/>
     </row>
     <row r="54" customFormat="1" spans="1:19">
-      <c r="A54" s="107"/>
-      <c r="B54" s="107"/>
+      <c r="A54" s="106"/>
+      <c r="B54" s="106"/>
       <c r="C54" s="168"/>
       <c r="D54" s="168"/>
       <c r="E54" s="168" t="s">
@@ -7440,7 +7434,7 @@
       <c r="N54" s="113"/>
       <c r="O54" s="171"/>
       <c r="P54" s="171"/>
-      <c r="Q54" s="107"/>
+      <c r="Q54" s="106"/>
       <c r="R54" s="89"/>
       <c r="S54" s="4"/>
     </row>
@@ -7501,7 +7495,7 @@
       <c r="S56" s="4"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="107" t="s">
+      <c r="A57" s="106" t="s">
         <v>65</v>
       </c>
       <c r="C57" s="168"/>
@@ -7521,8 +7515,8 @@
       <c r="S57" s="4"/>
     </row>
     <row r="58" customFormat="1" spans="1:19">
-      <c r="A58" s="107"/>
-      <c r="B58" s="107"/>
+      <c r="A58" s="106"/>
+      <c r="B58" s="106"/>
       <c r="C58" s="168"/>
       <c r="D58" s="168"/>
       <c r="E58" s="168"/>
@@ -7548,15 +7542,15 @@
       <c r="N58" s="113"/>
       <c r="O58" s="171"/>
       <c r="P58" s="171"/>
-      <c r="Q58" s="107"/>
+      <c r="Q58" s="106"/>
       <c r="R58" s="89" t="s">
         <v>66</v>
       </c>
       <c r="S58" s="4"/>
     </row>
     <row r="59" customFormat="1" spans="1:19">
-      <c r="A59" s="107"/>
-      <c r="B59" s="107"/>
+      <c r="A59" s="106"/>
+      <c r="B59" s="106"/>
       <c r="C59" s="168"/>
       <c r="D59" s="168" t="s">
         <v>67</v>
@@ -7584,13 +7578,13 @@
       <c r="N59" s="113"/>
       <c r="O59" s="171"/>
       <c r="P59" s="171"/>
-      <c r="Q59" s="107"/>
+      <c r="Q59" s="106"/>
       <c r="R59" s="89"/>
       <c r="S59" s="4"/>
     </row>
     <row r="60" customFormat="1" spans="1:19">
-      <c r="A60" s="107"/>
-      <c r="B60" s="107"/>
+      <c r="A60" s="106"/>
+      <c r="B60" s="106"/>
       <c r="C60" s="168"/>
       <c r="D60" s="168"/>
       <c r="E60" s="168"/>
@@ -7618,7 +7612,7 @@
       <c r="P60" s="171" t="s">
         <v>68</v>
       </c>
-      <c r="Q60" s="107"/>
+      <c r="Q60" s="106"/>
       <c r="R60" s="89"/>
       <c r="S60" s="4"/>
     </row>
@@ -7698,8 +7692,8 @@
       <c r="S63" s="4"/>
     </row>
     <row r="64" customFormat="1" spans="1:19">
-      <c r="A64" s="107"/>
-      <c r="B64" s="107"/>
+      <c r="A64" s="106"/>
+      <c r="B64" s="106"/>
       <c r="C64" s="168">
         <v>2080</v>
       </c>
@@ -7727,7 +7721,7 @@
       <c r="N64" s="113"/>
       <c r="O64" s="171"/>
       <c r="P64" s="171"/>
-      <c r="Q64" s="107"/>
+      <c r="Q64" s="106"/>
       <c r="R64" s="89"/>
       <c r="S64" s="4"/>
     </row>
@@ -7770,7 +7764,7 @@
       <c r="S66" s="4"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="107" t="s">
+      <c r="A67" s="106" t="s">
         <v>73</v>
       </c>
       <c r="C67" s="168"/>
@@ -7790,8 +7784,8 @@
       <c r="S67" s="4"/>
     </row>
     <row r="68" customFormat="1" spans="1:19">
-      <c r="A68" s="107"/>
-      <c r="B68" s="107"/>
+      <c r="A68" s="106"/>
+      <c r="B68" s="106"/>
       <c r="C68" s="168"/>
       <c r="D68" s="168"/>
       <c r="E68" s="168"/>
@@ -7819,13 +7813,13 @@
         <v>7600</v>
       </c>
       <c r="P68" s="171"/>
-      <c r="Q68" s="107"/>
+      <c r="Q68" s="106"/>
       <c r="R68" s="89"/>
       <c r="S68" s="4"/>
     </row>
     <row r="69" customFormat="1" spans="1:19">
-      <c r="A69" s="107"/>
-      <c r="B69" s="107"/>
+      <c r="A69" s="106"/>
+      <c r="B69" s="106"/>
       <c r="C69" s="168"/>
       <c r="D69" s="168"/>
       <c r="E69" s="168"/>
@@ -7853,13 +7847,13 @@
         <v>74</v>
       </c>
       <c r="P69" s="171"/>
-      <c r="Q69" s="107"/>
+      <c r="Q69" s="106"/>
       <c r="R69" s="89"/>
       <c r="S69" s="4"/>
     </row>
     <row r="70" customFormat="1" spans="1:19">
-      <c r="A70" s="107"/>
-      <c r="B70" s="107"/>
+      <c r="A70" s="106"/>
+      <c r="B70" s="106"/>
       <c r="C70" s="168"/>
       <c r="D70" s="168"/>
       <c r="E70" s="168"/>
@@ -7883,9 +7877,9 @@
       <c r="L70" s="113"/>
       <c r="M70" s="113"/>
       <c r="N70" s="113"/>
-      <c r="O70" s="107"/>
+      <c r="O70" s="106"/>
       <c r="P70" s="171"/>
-      <c r="Q70" s="107"/>
+      <c r="Q70" s="106"/>
       <c r="R70" s="89" t="s">
         <v>75</v>
       </c>
@@ -7947,7 +7941,7 @@
       <c r="S72" s="4"/>
     </row>
     <row r="73" spans="1:19">
-      <c r="A73" s="107">
+      <c r="A73" s="106">
         <v>5000</v>
       </c>
       <c r="C73" s="168"/>
@@ -7993,7 +7987,7 @@
       <c r="S74" s="4"/>
     </row>
     <row r="75" spans="1:19">
-      <c r="A75" s="107" t="s">
+      <c r="A75" s="106" t="s">
         <v>77</v>
       </c>
       <c r="C75" s="168"/>
@@ -8010,7 +8004,7 @@
       <c r="S75" s="4"/>
     </row>
     <row r="76" spans="1:19">
-      <c r="A76" s="107" t="s">
+      <c r="A76" s="106" t="s">
         <v>78</v>
       </c>
       <c r="C76" s="168"/>
@@ -8052,11 +8046,11 @@
       <c r="S77" s="4"/>
     </row>
     <row r="78" customFormat="1" spans="1:19">
-      <c r="A78" s="107"/>
+      <c r="A78" s="106"/>
       <c r="B78" s="119"/>
       <c r="C78" s="168"/>
       <c r="D78" s="168"/>
-      <c r="E78" s="107"/>
+      <c r="E78" s="106"/>
       <c r="F78" s="113"/>
       <c r="G78" s="150">
         <v>9958</v>
@@ -8077,22 +8071,22 @@
       <c r="L78" s="113"/>
       <c r="M78" s="113"/>
       <c r="N78" s="113"/>
-      <c r="O78" s="107"/>
+      <c r="O78" s="106"/>
       <c r="P78" s="171" t="s">
         <v>80</v>
       </c>
-      <c r="Q78" s="107"/>
+      <c r="Q78" s="106"/>
       <c r="R78" s="89"/>
       <c r="S78" s="4"/>
     </row>
     <row r="79" customFormat="1" spans="1:19">
-      <c r="A79" s="107"/>
+      <c r="A79" s="106"/>
       <c r="B79" s="119"/>
       <c r="C79" s="168">
         <v>2070</v>
       </c>
       <c r="D79" s="168"/>
-      <c r="E79" s="107"/>
+      <c r="E79" s="106"/>
       <c r="F79" s="113"/>
       <c r="G79" s="150">
         <v>9108</v>
@@ -8113,18 +8107,18 @@
       <c r="L79" s="113"/>
       <c r="M79" s="113"/>
       <c r="N79" s="113"/>
-      <c r="O79" s="107"/>
+      <c r="O79" s="106"/>
       <c r="P79" s="171"/>
       <c r="Q79" s="119"/>
       <c r="R79" s="89"/>
       <c r="S79" s="4"/>
     </row>
     <row r="80" customFormat="1" spans="1:19">
-      <c r="A80" s="107"/>
+      <c r="A80" s="106"/>
       <c r="B80" s="119"/>
       <c r="C80" s="168"/>
       <c r="D80" s="168"/>
-      <c r="E80" s="107"/>
+      <c r="E80" s="106"/>
       <c r="F80" s="113"/>
       <c r="G80" s="150">
         <v>9672</v>
@@ -8145,7 +8139,7 @@
       <c r="L80" s="113"/>
       <c r="M80" s="113"/>
       <c r="N80" s="113"/>
-      <c r="O80" s="107"/>
+      <c r="O80" s="106"/>
       <c r="P80" s="171" t="s">
         <v>81</v>
       </c>
@@ -8154,13 +8148,13 @@
       <c r="S80" s="4"/>
     </row>
     <row r="81" customFormat="1" spans="1:19">
-      <c r="A81" s="107"/>
+      <c r="A81" s="106"/>
       <c r="B81" s="119"/>
       <c r="C81" s="168"/>
       <c r="D81" s="168" t="s">
         <v>82</v>
       </c>
-      <c r="E81" s="107"/>
+      <c r="E81" s="106"/>
       <c r="F81" s="113"/>
       <c r="G81" s="150">
         <v>8924</v>
@@ -8181,20 +8175,20 @@
       <c r="L81" s="113"/>
       <c r="M81" s="113"/>
       <c r="N81" s="113"/>
-      <c r="O81" s="107"/>
+      <c r="O81" s="106"/>
       <c r="P81" s="171"/>
       <c r="Q81" s="119"/>
       <c r="R81" s="89"/>
       <c r="S81" s="4"/>
     </row>
     <row r="82" customFormat="1" spans="1:19">
-      <c r="A82" s="107"/>
+      <c r="A82" s="106"/>
       <c r="B82" s="119"/>
       <c r="C82" s="168"/>
       <c r="D82" s="168" t="s">
         <v>83</v>
       </c>
-      <c r="E82" s="107"/>
+      <c r="E82" s="106"/>
       <c r="F82" s="113"/>
       <c r="G82" s="150">
         <v>8783</v>
@@ -8215,20 +8209,20 @@
       <c r="L82" s="113"/>
       <c r="M82" s="113"/>
       <c r="N82" s="113"/>
-      <c r="O82" s="107"/>
+      <c r="O82" s="106"/>
       <c r="P82" s="171"/>
       <c r="Q82" s="119"/>
       <c r="R82" s="89"/>
       <c r="S82" s="4"/>
     </row>
     <row r="83" customFormat="1" spans="1:19">
-      <c r="A83" s="107"/>
+      <c r="A83" s="106"/>
       <c r="B83" s="119"/>
       <c r="C83" s="168" t="s">
         <v>84</v>
       </c>
       <c r="D83" s="168"/>
-      <c r="E83" s="107"/>
+      <c r="E83" s="106"/>
       <c r="F83" s="113"/>
       <c r="G83" s="150">
         <v>8752</v>
@@ -8249,7 +8243,7 @@
       <c r="L83" s="113"/>
       <c r="M83" s="113"/>
       <c r="N83" s="113"/>
-      <c r="O83" s="107"/>
+      <c r="O83" s="106"/>
       <c r="P83" s="171"/>
       <c r="Q83" s="119"/>
       <c r="R83" s="89"/>
@@ -8445,11 +8439,11 @@
       <c r="S90" s="4"/>
     </row>
     <row r="91" customFormat="1" spans="1:19">
-      <c r="A91" s="107"/>
+      <c r="A91" s="106"/>
       <c r="B91" s="168"/>
       <c r="C91" s="168"/>
       <c r="D91" s="168"/>
-      <c r="E91" s="107"/>
+      <c r="E91" s="106"/>
       <c r="F91" s="113"/>
       <c r="G91" s="150">
         <v>8295</v>
@@ -8470,7 +8464,7 @@
       <c r="L91" s="113"/>
       <c r="M91" s="113"/>
       <c r="N91" s="113"/>
-      <c r="O91" s="107"/>
+      <c r="O91" s="106"/>
       <c r="P91" s="171"/>
       <c r="Q91" s="171"/>
       <c r="R91" s="89"/>
@@ -12110,44 +12104,44 @@
       </c>
     </row>
     <row r="4" hidden="1" spans="2:16">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="105" t="s">
         <v>286</v>
       </c>
       <c r="C4" t="s">
         <v>287</v>
       </c>
-      <c r="O4" s="99">
+      <c r="O4" s="98">
         <v>450</v>
       </c>
     </row>
     <row r="5" hidden="1" spans="2:16">
-      <c r="B5" s="106"/>
+      <c r="B5" s="105"/>
       <c r="C5" t="s">
         <v>288</v>
       </c>
-      <c r="O5" s="99"/>
+      <c r="O5" s="98"/>
     </row>
     <row r="6" hidden="1" spans="2:16">
-      <c r="B6" s="106"/>
+      <c r="B6" s="105"/>
       <c r="C6" t="s">
         <v>289</v>
       </c>
-      <c r="O6" s="99">
+      <c r="O6" s="98">
         <v>450</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="106"/>
-      <c r="C7" s="111" t="s">
+      <c r="B7" s="105"/>
+      <c r="C7" s="110" t="s">
         <v>290</v>
       </c>
-      <c r="D7" s="99">
+      <c r="D7" s="98">
         <v>348</v>
       </c>
-      <c r="E7" s="99">
+      <c r="E7" s="98">
         <v>146</v>
       </c>
-      <c r="F7" s="99">
+      <c r="F7" s="98">
         <v>72</v>
       </c>
       <c r="I7" t="s">
@@ -12168,7 +12162,7 @@
       <c r="N7">
         <v>2730</v>
       </c>
-      <c r="O7" s="101">
+      <c r="O7" s="100">
         <v>400</v>
       </c>
       <c r="P7">
@@ -12176,7 +12170,7 @@
       </c>
     </row>
     <row r="8" hidden="1" spans="2:16">
-      <c r="B8" s="106"/>
+      <c r="B8" s="105"/>
       <c r="C8" t="s">
         <v>295</v>
       </c>
@@ -12186,7 +12180,7 @@
       <c r="H8" t="s">
         <v>281</v>
       </c>
-      <c r="O8" s="101">
+      <c r="O8" s="100">
         <v>400</v>
       </c>
       <c r="P8" s="126">
@@ -12194,7 +12188,7 @@
       </c>
     </row>
     <row r="9" hidden="1" spans="2:16">
-      <c r="B9" s="106"/>
+      <c r="B9" s="105"/>
       <c r="C9" t="s">
         <v>296</v>
       </c>
@@ -12204,7 +12198,7 @@
       <c r="H9" t="s">
         <v>281</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="100">
         <v>400</v>
       </c>
       <c r="P9" s="126">
@@ -12212,7 +12206,7 @@
       </c>
     </row>
     <row r="10" hidden="1" spans="2:16">
-      <c r="B10" s="106" t="s">
+      <c r="B10" s="105" t="s">
         <v>297</v>
       </c>
       <c r="C10" t="s">
@@ -12221,7 +12215,7 @@
       <c r="D10">
         <v>359</v>
       </c>
-      <c r="O10" s="101">
+      <c r="O10" s="100">
         <v>400</v>
       </c>
       <c r="P10" s="183" t="s">
@@ -12229,11 +12223,11 @@
       </c>
     </row>
     <row r="11" hidden="1" spans="2:16">
-      <c r="B11" s="106"/>
+      <c r="B11" s="105"/>
       <c r="C11" t="s">
         <v>300</v>
       </c>
-      <c r="O11" s="101">
+      <c r="O11" s="100">
         <v>400</v>
       </c>
       <c r="P11" s="126">
@@ -12241,17 +12235,17 @@
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="106"/>
-      <c r="C12" s="110" t="s">
+      <c r="B12" s="105"/>
+      <c r="C12" s="109" t="s">
         <v>301</v>
       </c>
-      <c r="D12" s="99">
+      <c r="D12" s="98">
         <v>338</v>
       </c>
-      <c r="E12" s="99">
+      <c r="E12" s="98">
         <v>140</v>
       </c>
-      <c r="F12" s="101">
+      <c r="F12" s="100">
         <v>50</v>
       </c>
       <c r="I12">
@@ -12272,7 +12266,7 @@
       <c r="N12">
         <v>2715</v>
       </c>
-      <c r="O12" s="101">
+      <c r="O12" s="100">
         <v>400</v>
       </c>
       <c r="P12">
@@ -12280,29 +12274,29 @@
       </c>
     </row>
     <row r="13" hidden="1" spans="2:16">
-      <c r="B13" s="106"/>
+      <c r="B13" s="105"/>
       <c r="C13" t="s">
         <v>305</v>
       </c>
       <c r="H13" t="s">
         <v>281</v>
       </c>
-      <c r="O13" s="111">
+      <c r="O13" s="110">
         <v>360</v>
       </c>
     </row>
     <row r="14" spans="2:16">
-      <c r="B14" s="106"/>
-      <c r="C14" s="111" t="s">
+      <c r="B14" s="105"/>
+      <c r="C14" s="110" t="s">
         <v>306</v>
       </c>
       <c r="D14" s="4">
         <v>303</v>
       </c>
-      <c r="E14" s="110">
+      <c r="E14" s="109">
         <v>121</v>
       </c>
-      <c r="F14" s="101">
+      <c r="F14" s="100">
         <v>49</v>
       </c>
       <c r="H14" t="s">
@@ -12326,7 +12320,7 @@
       <c r="N14">
         <v>2655</v>
       </c>
-      <c r="O14" s="111">
+      <c r="O14" s="110">
         <v>360</v>
       </c>
       <c r="P14">
@@ -12334,26 +12328,26 @@
       </c>
     </row>
     <row r="15" hidden="1" spans="2:16">
-      <c r="B15" s="106"/>
+      <c r="B15" s="105"/>
       <c r="C15" t="s">
         <v>309</v>
       </c>
       <c r="H15" t="s">
         <v>281</v>
       </c>
-      <c r="O15" s="110">
+      <c r="O15" s="109">
         <v>380</v>
       </c>
     </row>
     <row r="16" hidden="1" spans="2:16">
-      <c r="B16" s="106"/>
+      <c r="B16" s="105"/>
       <c r="C16" t="s">
         <v>310</v>
       </c>
       <c r="H16" t="s">
         <v>281</v>
       </c>
-      <c r="O16" s="111">
+      <c r="O16" s="110">
         <v>360</v>
       </c>
       <c r="P16" s="126">
@@ -12361,40 +12355,40 @@
       </c>
     </row>
     <row r="17" hidden="1" spans="2:17">
-      <c r="B17" s="106" t="s">
+      <c r="B17" s="105" t="s">
         <v>311</v>
       </c>
       <c r="C17" t="s">
         <v>312</v>
       </c>
-      <c r="O17" s="99">
+      <c r="O17" s="98">
         <v>450</v>
       </c>
     </row>
     <row r="18" hidden="1" spans="2:17">
-      <c r="B18" s="106"/>
+      <c r="B18" s="105"/>
       <c r="C18" t="s">
         <v>313</v>
       </c>
-      <c r="O18" s="99">
+      <c r="O18" s="98">
         <v>450</v>
       </c>
     </row>
     <row r="19" hidden="1" spans="2:17">
-      <c r="B19" s="106"/>
+      <c r="B19" s="105"/>
       <c r="C19" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="20" hidden="1" spans="2:17">
-      <c r="B20" s="106"/>
+      <c r="B20" s="105"/>
       <c r="C20" t="s">
         <v>315</v>
       </c>
       <c r="H20" t="s">
         <v>281</v>
       </c>
-      <c r="O20" s="101">
+      <c r="O20" s="100">
         <v>400</v>
       </c>
       <c r="P20">
@@ -12405,17 +12399,17 @@
       </c>
     </row>
     <row r="21" spans="2:17">
-      <c r="B21" s="106"/>
-      <c r="C21" s="110" t="s">
+      <c r="B21" s="105"/>
+      <c r="C21" s="109" t="s">
         <v>317</v>
       </c>
       <c r="D21">
         <v>304</v>
       </c>
-      <c r="E21" s="110">
+      <c r="E21" s="109">
         <v>126</v>
       </c>
-      <c r="F21" s="101">
+      <c r="F21" s="100">
         <v>50</v>
       </c>
       <c r="H21" t="s">
@@ -12439,7 +12433,7 @@
       <c r="N21">
         <v>2670</v>
       </c>
-      <c r="O21" s="101">
+      <c r="O21" s="100">
         <v>400</v>
       </c>
       <c r="P21">
@@ -12447,13 +12441,13 @@
       </c>
     </row>
     <row r="22" spans="2:17">
-      <c r="B22" s="106" t="s">
+      <c r="B22" s="105" t="s">
         <v>320</v>
       </c>
       <c r="C22" t="s">
         <v>321</v>
       </c>
-      <c r="O22" s="101">
+      <c r="O22" s="100">
         <v>400</v>
       </c>
       <c r="P22" s="126">
@@ -12461,17 +12455,17 @@
       </c>
     </row>
     <row r="23" spans="2:17">
-      <c r="B23" s="106"/>
+      <c r="B23" s="105"/>
       <c r="C23" t="s">
         <v>322</v>
       </c>
-      <c r="O23" s="101">
+      <c r="O23" s="100">
         <v>400</v>
       </c>
       <c r="P23" s="126"/>
     </row>
     <row r="24" spans="2:17">
-      <c r="B24" s="106"/>
+      <c r="B24" s="105"/>
       <c r="C24" t="s">
         <v>323</v>
       </c>
@@ -12483,11 +12477,11 @@
       </c>
     </row>
     <row r="25" spans="2:17">
-      <c r="B25" s="106"/>
+      <c r="B25" s="105"/>
       <c r="C25" t="s">
         <v>324</v>
       </c>
-      <c r="O25" s="110">
+      <c r="O25" s="109">
         <v>380</v>
       </c>
       <c r="P25" s="126">
@@ -12793,23 +12787,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:W42"/>
+  <dimension ref="B1:U42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="12.0185185185185" customWidth="1"/>
-    <col min="3" max="3" width="12.2037037037037" style="107" customWidth="1"/>
+    <col min="3" max="3" width="12.2037037037037" style="106" customWidth="1"/>
     <col min="5" max="5" width="8.24074074074074" customWidth="1"/>
     <col min="6" max="11" width="9" customWidth="1"/>
     <col min="13" max="13" width="9" customWidth="1"/>
-    <col min="16" max="17" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23">
+    <row r="1" spans="2:21">
+      <c r="F1">
+        <v>2025</v>
+      </c>
       <c r="N1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="2:23">
+    <row r="2" spans="2:21">
       <c r="F2">
         <v>1</v>
       </c>
@@ -12840,36 +12836,30 @@
       <c r="P2" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="Q2">
+        <v>8</v>
+      </c>
+      <c r="R2">
+        <v>9</v>
+      </c>
+      <c r="S2">
+        <v>10</v>
+      </c>
+      <c r="T2">
+        <v>11</v>
+      </c>
+      <c r="U2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21">
+      <c r="B3" s="107" t="s">
         <v>337</v>
       </c>
-      <c r="R2" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="S2">
-        <v>8</v>
-      </c>
-      <c r="T2">
-        <v>9</v>
-      </c>
-      <c r="U2">
-        <v>10</v>
-      </c>
-      <c r="V2">
-        <v>11</v>
-      </c>
-      <c r="W2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="2:23">
-      <c r="B3" s="108" t="s">
-        <v>339</v>
-      </c>
-      <c r="C3" s="107">
+      <c r="C3" s="106">
         <v>5090</v>
       </c>
-      <c r="D3" s="109">
+      <c r="D3" s="108">
         <v>125801</v>
       </c>
       <c r="E3">
@@ -12885,15 +12875,15 @@
       <c r="J3">
         <v>26588</v>
       </c>
-      <c r="K3" s="110">
+      <c r="K3" s="109">
         <v>21500</v>
       </c>
-      <c r="L3" s="110">
+      <c r="L3" s="109">
         <v>20599</v>
       </c>
-      <c r="M3" s="1">
-        <f>N3-L3</f>
-        <v>10889</v>
+      <c r="M3" s="1" t="str">
+        <f>TEXT((S3-L3)/L3,"0.0%")</f>
+        <v>130.6%</v>
       </c>
       <c r="N3">
         <v>31488</v>
@@ -12901,30 +12891,25 @@
       <c r="O3">
         <v>31999</v>
       </c>
-      <c r="P3" s="1">
-        <f>R3-L3</f>
-        <v>10400</v>
+      <c r="P3">
+        <v>30999</v>
       </c>
       <c r="Q3">
-        <f>R3-O3</f>
-        <v>-1000</v>
+        <v>35099</v>
       </c>
       <c r="R3">
-        <v>30999</v>
+        <v>40000</v>
       </c>
       <c r="S3">
-        <v>35099</v>
-      </c>
-      <c r="T3">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="4" spans="2:23">
-      <c r="B4" s="108"/>
-      <c r="C4" s="107" t="s">
+        <v>47500</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21">
+      <c r="B4" s="107"/>
+      <c r="C4" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="109">
+      <c r="D4" s="108">
         <v>125801</v>
       </c>
       <c r="E4">
@@ -12946,12 +12931,12 @@
       <c r="K4">
         <v>26899</v>
       </c>
-      <c r="L4" s="111">
+      <c r="L4" s="110">
         <v>21399</v>
       </c>
-      <c r="M4" s="1">
-        <f t="shared" ref="M4:M32" si="0">N4-L4</f>
-        <v>6570</v>
+      <c r="M4" s="1" t="str">
+        <f>TEXT((S4-L4)/L4,"0.0%")</f>
+        <v>95.3%</v>
       </c>
       <c r="N4">
         <v>27969</v>
@@ -12959,30 +12944,25 @@
       <c r="O4">
         <v>28999</v>
       </c>
-      <c r="P4" s="1">
-        <f t="shared" ref="P4:P12" si="1">R4-L4</f>
-        <v>9600</v>
-      </c>
-      <c r="Q4" s="1">
-        <f t="shared" ref="Q4:Q12" si="2">R4-O4</f>
-        <v>2000</v>
+      <c r="P4">
+        <v>30999</v>
+      </c>
+      <c r="Q4">
+        <v>33999</v>
       </c>
       <c r="R4">
-        <v>30999</v>
+        <v>38000</v>
       </c>
       <c r="S4">
-        <v>33999</v>
-      </c>
-      <c r="T4">
-        <v>38000</v>
-      </c>
-    </row>
-    <row r="5" spans="2:23">
-      <c r="B5" s="108"/>
-      <c r="C5" s="107" t="s">
+        <v>41800</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21">
+      <c r="B5" s="107"/>
+      <c r="C5" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="109">
+      <c r="D5" s="108">
         <v>119443</v>
       </c>
       <c r="E5">
@@ -12990,215 +12970,200 @@
         <v>6.43238731218698</v>
       </c>
       <c r="L5" s="4"/>
-      <c r="N5" s="111">
+      <c r="M5" s="111"/>
+      <c r="N5" s="110">
         <v>18569</v>
       </c>
-      <c r="O5" s="110">
+      <c r="O5" s="109">
         <v>18700</v>
       </c>
-      <c r="Q5" s="1">
-        <f t="shared" si="2"/>
-        <v>2564</v>
+      <c r="P5">
+        <v>21264</v>
+      </c>
+      <c r="Q5">
+        <v>21794</v>
       </c>
       <c r="R5">
-        <v>21264</v>
+        <v>26000</v>
       </c>
       <c r="S5">
-        <v>21794</v>
-      </c>
-      <c r="T5">
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:23">
-      <c r="B6" s="108"/>
-      <c r="C6" s="107">
+        <v>26500</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21">
+      <c r="B6" s="107"/>
+      <c r="C6" s="106">
         <v>5080</v>
       </c>
       <c r="D6" s="2">
         <v>78535</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:E40" si="3">ROUND(D6/L6,2)</f>
+        <f t="shared" ref="E6:E40" si="0">ROUND(D6/L6,2)</f>
         <v>8.73</v>
       </c>
       <c r="G6">
         <v>9899</v>
       </c>
-      <c r="H6" s="110">
+      <c r="H6" s="109">
         <v>9795</v>
       </c>
-      <c r="I6" s="111">
+      <c r="I6" s="110">
         <v>8798</v>
       </c>
-      <c r="J6" s="111">
+      <c r="J6" s="110">
         <v>8599</v>
       </c>
-      <c r="K6" s="111">
+      <c r="K6" s="110">
         <v>8899</v>
       </c>
-      <c r="L6" s="111">
+      <c r="L6" s="110">
         <v>8999</v>
       </c>
-      <c r="M6" s="5">
-        <f t="shared" si="0"/>
-        <v>-457</v>
-      </c>
-      <c r="N6" s="111">
+      <c r="M6" s="1" t="str">
+        <f>TEXT((S6-L6)/L6,"0.0%")</f>
+        <v>44.5%</v>
+      </c>
+      <c r="N6" s="110">
         <v>8542</v>
       </c>
-      <c r="O6" s="110">
+      <c r="O6" s="109">
         <v>8740</v>
       </c>
-      <c r="P6" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="Q6" s="1">
-        <f t="shared" si="2"/>
-        <v>1259</v>
+      <c r="P6">
+        <v>9999</v>
+      </c>
+      <c r="Q6">
+        <v>10198</v>
       </c>
       <c r="R6">
-        <v>9999</v>
+        <v>12500</v>
       </c>
       <c r="S6">
-        <v>10198</v>
-      </c>
-      <c r="T6">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="7" spans="2:23">
-      <c r="B7" s="108"/>
-      <c r="C7" s="107" t="s">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21">
+      <c r="B7" s="107"/>
+      <c r="C7" s="106" t="s">
         <v>34</v>
       </c>
       <c r="D7" s="2">
         <v>66857</v>
       </c>
       <c r="E7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>9.8</v>
       </c>
-      <c r="H7" s="111">
+      <c r="H7" s="110">
         <v>7189</v>
       </c>
-      <c r="I7" s="111">
+      <c r="I7" s="110">
         <v>6578</v>
       </c>
-      <c r="J7" s="111">
+      <c r="J7" s="110">
         <v>6579</v>
       </c>
-      <c r="K7" s="111">
+      <c r="K7" s="110">
         <v>6599</v>
       </c>
-      <c r="L7" s="111">
+      <c r="L7" s="110">
         <v>6819</v>
       </c>
-      <c r="M7">
-        <f t="shared" si="0"/>
-        <v>-48</v>
-      </c>
-      <c r="N7" s="111">
+      <c r="M7" s="1" t="str">
+        <f>TEXT((S7-L7)/L7,"0.0%")</f>
+        <v>39.3%</v>
+      </c>
+      <c r="N7" s="110">
         <v>6771</v>
       </c>
       <c r="O7">
         <v>7128</v>
       </c>
-      <c r="P7" s="1">
-        <f t="shared" si="1"/>
-        <v>980</v>
-      </c>
-      <c r="Q7" s="1">
-        <f t="shared" si="2"/>
-        <v>671</v>
+      <c r="P7">
+        <v>7799</v>
+      </c>
+      <c r="Q7">
+        <v>8314</v>
       </c>
       <c r="R7">
-        <v>7799</v>
+        <v>9000</v>
       </c>
       <c r="S7">
-        <v>8314</v>
-      </c>
-      <c r="T7">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="8" spans="2:23">
-      <c r="B8" s="108"/>
-      <c r="C8" s="107">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21">
+      <c r="B8" s="107"/>
+      <c r="C8" s="106">
         <v>5070</v>
       </c>
       <c r="D8" s="3">
         <v>52209</v>
       </c>
       <c r="E8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>11.71</v>
       </c>
-      <c r="I8" s="111">
+      <c r="I8" s="110">
         <v>4761</v>
       </c>
-      <c r="J8" s="110">
+      <c r="J8" s="109">
         <v>4569</v>
       </c>
-      <c r="K8" s="111">
+      <c r="K8" s="110">
         <v>4628</v>
       </c>
-      <c r="L8" s="111">
+      <c r="L8" s="110">
         <v>4459</v>
       </c>
-      <c r="M8">
-        <f t="shared" si="0"/>
-        <v>-60</v>
-      </c>
-      <c r="N8" s="111">
+      <c r="M8" s="1" t="str">
+        <f>TEXT((S8-L8)/L8,"0.0%")</f>
+        <v>59.2%</v>
+      </c>
+      <c r="N8" s="110">
         <v>4399</v>
       </c>
       <c r="O8">
         <v>4799</v>
       </c>
-      <c r="P8" s="1">
-        <f t="shared" si="1"/>
-        <v>1040</v>
-      </c>
-      <c r="Q8" s="1">
-        <f t="shared" si="2"/>
-        <v>700</v>
+      <c r="P8">
+        <v>5499</v>
+      </c>
+      <c r="Q8">
+        <v>5779</v>
       </c>
       <c r="R8">
-        <v>5499</v>
+        <v>6600</v>
       </c>
       <c r="S8">
-        <v>5779</v>
-      </c>
-      <c r="T8">
-        <v>6600</v>
-      </c>
-    </row>
-    <row r="9" spans="2:23">
-      <c r="B9" s="108"/>
-      <c r="C9" s="107" t="s">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21">
+      <c r="B9" s="107"/>
+      <c r="C9" s="106" t="s">
         <v>54</v>
       </c>
       <c r="D9" s="5">
         <v>35924</v>
       </c>
       <c r="E9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>9.98</v>
       </c>
-      <c r="J9" s="111">
+      <c r="J9" s="110">
         <v>3599</v>
       </c>
-      <c r="K9" s="111">
+      <c r="K9" s="110">
         <v>3599</v>
       </c>
-      <c r="L9" s="110">
+      <c r="L9" s="109">
         <v>3599</v>
       </c>
-      <c r="M9" s="1">
-        <f t="shared" si="0"/>
-        <v>100</v>
+      <c r="M9" s="1" t="str">
+        <f>TEXT((S9-L9)/L9,"0.0%")</f>
+        <v>50.0%</v>
       </c>
       <c r="N9" s="4">
         <v>3699</v>
@@ -13206,121 +13171,106 @@
       <c r="O9">
         <v>3715</v>
       </c>
-      <c r="P9" s="1">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="Q9" s="1">
-        <f t="shared" si="2"/>
-        <v>884</v>
+      <c r="P9">
+        <v>4599</v>
+      </c>
+      <c r="Q9">
+        <v>4899</v>
       </c>
       <c r="R9">
-        <v>4599</v>
+        <v>5300</v>
       </c>
       <c r="S9">
-        <v>4899</v>
-      </c>
-      <c r="T9">
-        <v>5300</v>
-      </c>
-    </row>
-    <row r="10" spans="2:23">
-      <c r="B10" s="108"/>
-      <c r="C10" s="107" t="s">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21">
+      <c r="B10" s="107"/>
+      <c r="C10" s="106" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="5">
         <v>35924</v>
       </c>
       <c r="E10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>11.59</v>
       </c>
-      <c r="J10" s="111">
+      <c r="J10" s="110">
         <v>3199</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="109">
         <v>3266</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="110">
         <v>3099</v>
       </c>
-      <c r="M10" s="5">
-        <f t="shared" si="0"/>
-        <v>-401</v>
-      </c>
-      <c r="N10" s="111">
+      <c r="M10" s="3" t="str">
+        <f>TEXT((S10-L10)/L10,"0.0%")</f>
+        <v>19.4%</v>
+      </c>
+      <c r="N10" s="110">
         <v>2698</v>
       </c>
-      <c r="O10" s="110">
+      <c r="O10" s="109">
         <v>2899</v>
       </c>
-      <c r="P10" s="1">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="Q10" s="1">
-        <f t="shared" si="2"/>
-        <v>300</v>
+      <c r="P10">
+        <v>3199</v>
+      </c>
+      <c r="Q10">
+        <v>3299</v>
       </c>
       <c r="R10">
-        <v>3199</v>
+        <v>3500</v>
       </c>
       <c r="S10">
-        <v>3299</v>
-      </c>
-      <c r="T10">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="11" spans="2:23">
-      <c r="B11" s="108"/>
-      <c r="C11" s="107">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21">
+      <c r="B11" s="107"/>
+      <c r="C11" s="106">
         <v>5060</v>
       </c>
       <c r="D11" s="112">
         <v>32816</v>
       </c>
       <c r="E11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>13.13</v>
       </c>
-      <c r="K11" s="110">
+      <c r="K11" s="109">
         <v>2648</v>
       </c>
-      <c r="L11" s="111">
+      <c r="L11" s="110">
         <v>2499</v>
       </c>
-      <c r="M11" s="5">
-        <f t="shared" si="0"/>
-        <v>-211</v>
-      </c>
-      <c r="N11" s="111">
+      <c r="M11" s="1" t="str">
+        <f>TEXT((S11-L11)/L11,"0.0%")</f>
+        <v>32.1%</v>
+      </c>
+      <c r="N11" s="110">
         <v>2288</v>
       </c>
-      <c r="O11" s="110">
+      <c r="O11" s="109">
         <v>2379</v>
       </c>
-      <c r="P11" s="1">
-        <f t="shared" si="1"/>
-        <v>191</v>
-      </c>
-      <c r="Q11" s="1">
-        <f t="shared" si="2"/>
-        <v>311</v>
+      <c r="P11">
+        <v>2690</v>
+      </c>
+      <c r="Q11">
+        <v>2801</v>
       </c>
       <c r="R11">
-        <v>2690</v>
+        <v>3000</v>
       </c>
       <c r="S11">
-        <v>2801</v>
-      </c>
-      <c r="T11">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="12" spans="2:23">
-      <c r="B12" s="108"/>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21">
+      <c r="B12" s="107"/>
       <c r="C12" s="113">
         <v>5050</v>
       </c>
@@ -13328,45 +13278,40 @@
         <v>23537</v>
       </c>
       <c r="E12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>11.21</v>
       </c>
       <c r="L12">
         <v>2099</v>
       </c>
-      <c r="M12" s="5">
-        <f t="shared" si="0"/>
-        <v>-310</v>
-      </c>
-      <c r="N12" s="111">
+      <c r="M12" s="2" t="str">
+        <f>TEXT((S12-L12)/L12,"0.0%")</f>
+        <v>23.9%</v>
+      </c>
+      <c r="N12" s="110">
         <v>1789</v>
       </c>
       <c r="O12">
         <v>1879</v>
       </c>
       <c r="P12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <f t="shared" si="2"/>
-        <v>220</v>
+        <v>2099</v>
+      </c>
+      <c r="Q12">
+        <v>2224</v>
       </c>
       <c r="R12">
-        <v>2099</v>
+        <v>2500</v>
       </c>
       <c r="S12">
-        <v>2224</v>
-      </c>
-      <c r="T12">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="13" spans="2:23">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21">
       <c r="B13" s="115" t="s">
-        <v>340</v>
-      </c>
-      <c r="C13" s="107">
+        <v>338</v>
+      </c>
+      <c r="C13" s="106">
         <v>4090</v>
       </c>
       <c r="D13" s="116">
@@ -13387,10 +13332,11 @@
       <c r="J13">
         <v>22500</v>
       </c>
-    </row>
-    <row r="14" spans="2:23">
+      <c r="M13" s="111"/>
+    </row>
+    <row r="14" spans="2:21">
       <c r="B14" s="117"/>
-      <c r="C14" s="107" t="s">
+      <c r="C14" s="106" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="116">
@@ -13411,10 +13357,11 @@
       <c r="J14">
         <v>18000</v>
       </c>
-    </row>
-    <row r="15" spans="2:23">
+      <c r="M14" s="111"/>
+    </row>
+    <row r="15" spans="2:21">
       <c r="B15" s="117"/>
-      <c r="C15" s="107" t="s">
+      <c r="C15" s="106" t="s">
         <v>33</v>
       </c>
       <c r="D15" s="2">
@@ -13423,7 +13370,7 @@
       <c r="F15">
         <v>7254</v>
       </c>
-      <c r="G15" s="110">
+      <c r="G15" s="109">
         <v>7299</v>
       </c>
       <c r="H15">
@@ -13435,41 +13382,43 @@
       <c r="J15">
         <v>8899</v>
       </c>
-    </row>
-    <row r="16" spans="2:23">
+      <c r="M15" s="111"/>
+    </row>
+    <row r="16" spans="2:21">
       <c r="B16" s="117"/>
-      <c r="C16" s="107" t="s">
+      <c r="C16" s="106" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="3">
         <v>57038</v>
       </c>
-      <c r="F16" s="110">
+      <c r="F16" s="109">
         <v>5588</v>
       </c>
-      <c r="G16" s="110">
+      <c r="G16" s="109">
         <v>5549</v>
       </c>
-      <c r="H16" s="110">
+      <c r="H16" s="109">
         <v>5948</v>
       </c>
       <c r="I16">
         <v>5999</v>
       </c>
-    </row>
-    <row r="17" spans="2:20">
+      <c r="M16" s="111"/>
+    </row>
+    <row r="17" spans="2:19">
       <c r="B17" s="117"/>
-      <c r="C17" s="107" t="s">
+      <c r="C17" s="106" t="s">
         <v>43</v>
       </c>
       <c r="D17" s="3">
         <v>49052</v>
       </c>
       <c r="E17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>11.42</v>
       </c>
-      <c r="F17" s="111">
+      <c r="F17" s="110">
         <v>4699</v>
       </c>
       <c r="G17">
@@ -13481,29 +13430,30 @@
       <c r="I17">
         <v>4589</v>
       </c>
-      <c r="J17" s="111">
+      <c r="J17" s="110">
         <v>4199</v>
       </c>
-      <c r="K17" s="111">
+      <c r="K17" s="110">
         <v>4199</v>
       </c>
       <c r="L17">
         <v>4294</v>
       </c>
-    </row>
-    <row r="18" spans="2:20">
+      <c r="M17" s="111"/>
+    </row>
+    <row r="18" spans="2:19">
       <c r="B18" s="117"/>
-      <c r="C18" s="107">
+      <c r="C18" s="106">
         <v>4070</v>
       </c>
       <c r="D18" s="3">
         <v>41204</v>
       </c>
       <c r="E18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>11.45</v>
       </c>
-      <c r="F18" s="110">
+      <c r="F18" s="109">
         <v>3889</v>
       </c>
       <c r="G18">
@@ -13524,48 +13474,50 @@
       <c r="L18">
         <v>3599</v>
       </c>
-    </row>
-    <row r="19" spans="2:20">
+      <c r="M18" s="111"/>
+    </row>
+    <row r="19" spans="2:19">
       <c r="B19" s="117"/>
-      <c r="C19" s="107" t="s">
+      <c r="C19" s="106" t="s">
         <v>61</v>
       </c>
       <c r="D19" s="5">
         <v>30861</v>
       </c>
       <c r="E19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>10.65</v>
       </c>
-      <c r="F19" s="110">
+      <c r="F19" s="109">
         <v>3402</v>
       </c>
       <c r="G19">
         <v>3699</v>
       </c>
-      <c r="H19" s="110">
+      <c r="H19" s="109">
         <v>3519</v>
       </c>
-      <c r="I19" s="110">
+      <c r="I19" s="109">
         <v>3650</v>
       </c>
-      <c r="L19" s="110">
+      <c r="L19" s="109">
         <v>2899</v>
       </c>
-    </row>
-    <row r="20" spans="2:20">
+      <c r="M19" s="111"/>
+    </row>
+    <row r="20" spans="2:19">
       <c r="B20" s="117"/>
-      <c r="C20" s="107" t="s">
+      <c r="C20" s="106" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="5">
         <v>30861</v>
       </c>
       <c r="E20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>13.42</v>
       </c>
-      <c r="F20" s="110">
+      <c r="F20" s="109">
         <v>2945</v>
       </c>
       <c r="G20">
@@ -13574,7 +13526,7 @@
       <c r="H20">
         <v>3219</v>
       </c>
-      <c r="I20" s="110">
+      <c r="I20" s="109">
         <v>2999</v>
       </c>
       <c r="J20">
@@ -13586,26 +13538,27 @@
       <c r="L20">
         <v>2299</v>
       </c>
-    </row>
-    <row r="21" spans="2:20">
+      <c r="M20" s="111"/>
+    </row>
+    <row r="21" spans="2:19">
       <c r="B21" s="117"/>
-      <c r="C21" s="107">
+      <c r="C21" s="106">
         <v>4060</v>
       </c>
       <c r="D21" s="118">
         <v>23865</v>
       </c>
       <c r="E21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>10.87</v>
       </c>
-      <c r="F21" s="110">
+      <c r="F21" s="109">
         <v>2014</v>
       </c>
-      <c r="G21" s="110">
+      <c r="G21" s="109">
         <v>2061</v>
       </c>
-      <c r="H21" s="110">
+      <c r="H21" s="109">
         <v>2229</v>
       </c>
       <c r="I21">
@@ -13620,10 +13573,11 @@
       <c r="L21">
         <v>2195</v>
       </c>
-    </row>
-    <row r="22" s="4" customFormat="1" spans="2:20">
-      <c r="B22" s="98" t="s">
-        <v>341</v>
+      <c r="M21" s="111"/>
+    </row>
+    <row r="22" s="4" customFormat="1" spans="2:19">
+      <c r="B22" s="97" t="s">
+        <v>339</v>
       </c>
       <c r="C22" s="119" t="s">
         <v>28</v>
@@ -13632,51 +13586,46 @@
         <v>68953</v>
       </c>
       <c r="E22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>13.79</v>
       </c>
-      <c r="I22" s="99">
+      <c r="I22" s="98">
         <v>5499</v>
       </c>
-      <c r="J22" s="99">
+      <c r="J22" s="98">
         <v>5289</v>
       </c>
-      <c r="K22" s="99">
+      <c r="K22" s="98">
         <v>5289</v>
       </c>
-      <c r="L22" s="99">
+      <c r="L22" s="98">
         <v>4999</v>
       </c>
-      <c r="M22" s="5">
-        <f t="shared" si="0"/>
-        <v>-876</v>
-      </c>
-      <c r="N22" s="99">
+      <c r="M22" s="2" t="str">
+        <f>TEXT((S22-L22)/L22,"0.0%")</f>
+        <v>22.0%</v>
+      </c>
+      <c r="N22" s="98">
         <v>4123</v>
       </c>
-      <c r="O22" s="99">
+      <c r="O22" s="98">
         <v>4199</v>
       </c>
-      <c r="P22" s="5">
-        <f>R22-L22</f>
-        <v>-200</v>
-      </c>
-      <c r="Q22" s="1">
-        <f>R22-O22</f>
-        <v>600</v>
+      <c r="P22" s="4">
+        <v>4799</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>5199</v>
       </c>
       <c r="R22" s="4">
-        <v>4799</v>
+        <v>5700</v>
       </c>
       <c r="S22" s="4">
-        <v>5199</v>
-      </c>
-      <c r="T22" s="4">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="23" s="4" customFormat="1" spans="2:20">
-      <c r="B23" s="98"/>
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="23" s="4" customFormat="1" spans="2:19">
+      <c r="B23" s="97"/>
       <c r="C23" s="119">
         <v>9070</v>
       </c>
@@ -13684,196 +13633,176 @@
         <v>60503</v>
       </c>
       <c r="E23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>13.66</v>
       </c>
-      <c r="I23" s="99">
+      <c r="I23" s="98">
         <v>4750</v>
       </c>
-      <c r="J23" s="99">
+      <c r="J23" s="98">
         <v>4599</v>
       </c>
-      <c r="K23" s="99">
+      <c r="K23" s="98">
         <v>4438</v>
       </c>
-      <c r="L23" s="99">
+      <c r="L23" s="98">
         <v>4429</v>
       </c>
-      <c r="M23" s="5">
-        <f t="shared" si="0"/>
-        <v>-670</v>
-      </c>
-      <c r="N23" s="101">
+      <c r="M23" s="2" t="str">
+        <f>TEXT((S23-L23)/L23,"0.0%")</f>
+        <v>21.9%</v>
+      </c>
+      <c r="N23" s="100">
         <v>3759</v>
       </c>
       <c r="O23" s="4">
         <v>3861</v>
       </c>
-      <c r="P23">
-        <f>R23-L23</f>
-        <v>-30</v>
-      </c>
-      <c r="Q23" s="1">
-        <f>R23-O23</f>
-        <v>538</v>
+      <c r="P23" s="4">
+        <v>4399</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>4689</v>
       </c>
       <c r="R23" s="4">
-        <v>4399</v>
+        <v>5200</v>
       </c>
       <c r="S23" s="4">
-        <v>4689</v>
-      </c>
-      <c r="T23" s="4">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="2:20">
-      <c r="B24" s="98"/>
-      <c r="C24" s="107" t="s">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="2:19">
+      <c r="B24" s="97"/>
+      <c r="C24" s="106" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="3">
         <v>52384</v>
       </c>
       <c r="E24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>14.6</v>
       </c>
       <c r="J24">
         <v>3899</v>
       </c>
-      <c r="K24" s="101">
+      <c r="K24" s="100">
         <v>3699</v>
       </c>
-      <c r="L24" s="99">
+      <c r="L24" s="98">
         <v>3589</v>
       </c>
-      <c r="M24" s="5">
-        <f t="shared" si="0"/>
-        <v>-660</v>
-      </c>
-      <c r="N24" s="99">
+      <c r="M24" s="3" t="str">
+        <f>TEXT((S24-L24)/L24,"0.0%")</f>
+        <v>17.0%</v>
+      </c>
+      <c r="N24" s="98">
         <v>2929</v>
       </c>
-      <c r="O24" s="101">
+      <c r="O24" s="100">
         <v>3300</v>
       </c>
       <c r="P24">
-        <f>R24-L24</f>
-        <v>-90</v>
-      </c>
-      <c r="Q24" s="1">
-        <f>R24-O24</f>
-        <v>199</v>
+        <v>3499</v>
+      </c>
+      <c r="Q24">
+        <v>3688</v>
       </c>
       <c r="R24">
-        <v>3499</v>
+        <v>3900</v>
       </c>
       <c r="S24">
-        <v>3688</v>
-      </c>
-      <c r="T24">
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="2:20">
-      <c r="B25" s="98"/>
-      <c r="C25" s="107" t="s">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="2:19">
+      <c r="B25" s="97"/>
+      <c r="C25" s="106" t="s">
         <v>51</v>
       </c>
       <c r="D25" s="5">
         <v>37402</v>
       </c>
       <c r="E25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>13.66</v>
       </c>
       <c r="L25">
         <v>2739</v>
       </c>
-      <c r="M25" s="5">
-        <f t="shared" si="0"/>
-        <v>-439</v>
-      </c>
-      <c r="N25" s="99">
+      <c r="M25" s="1" t="str">
+        <f>TEXT((S25-L25)/L25,"0.0%")</f>
+        <v>31.4%</v>
+      </c>
+      <c r="N25" s="98">
         <v>2300</v>
       </c>
-      <c r="O25" s="101">
+      <c r="O25" s="100">
         <v>2448</v>
       </c>
       <c r="P25">
-        <f>R25-L25</f>
-        <v>55</v>
-      </c>
-      <c r="Q25" s="1">
-        <f>R25-O25</f>
-        <v>346</v>
+        <v>2794</v>
+      </c>
+      <c r="Q25">
+        <v>3075</v>
       </c>
       <c r="R25">
-        <v>2794</v>
+        <v>3300</v>
       </c>
       <c r="S25">
-        <v>3075</v>
-      </c>
-      <c r="T25">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="2:20">
-      <c r="B26" s="98"/>
-      <c r="C26" s="107" t="s">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="2:19">
+      <c r="B26" s="97"/>
+      <c r="C26" s="106" t="s">
         <v>56</v>
       </c>
       <c r="D26" s="5">
         <v>35550</v>
       </c>
       <c r="E26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>15.46</v>
       </c>
       <c r="L26">
         <v>2299</v>
       </c>
-      <c r="M26">
-        <f t="shared" si="0"/>
-        <v>-275</v>
-      </c>
-      <c r="N26" s="101">
+      <c r="M26" s="2" t="str">
+        <f>TEXT((S26-L26)/L26,"0.0%")</f>
+        <v>21.8%</v>
+      </c>
+      <c r="N26" s="100">
         <v>2024</v>
       </c>
       <c r="O26">
         <v>2188</v>
       </c>
-      <c r="P26" s="5">
-        <f>R26-L26</f>
-        <v>-100</v>
+      <c r="P26">
+        <v>2199</v>
       </c>
       <c r="Q26">
-        <f>R26-O26</f>
-        <v>11</v>
+        <v>2450</v>
       </c>
       <c r="R26">
-        <v>2199</v>
+        <v>2600</v>
       </c>
       <c r="S26">
-        <v>2450</v>
-      </c>
-      <c r="T26">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20">
-      <c r="B27" s="102" t="s">
-        <v>342</v>
-      </c>
-      <c r="C27" s="107" t="s">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19">
+      <c r="B27" s="101" t="s">
+        <v>340</v>
+      </c>
+      <c r="C27" s="106" t="s">
         <v>30</v>
       </c>
       <c r="D27" s="2">
         <v>68852</v>
       </c>
       <c r="E27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>11.48</v>
       </c>
       <c r="F27">
@@ -13897,23 +13826,24 @@
       <c r="L27">
         <v>5999</v>
       </c>
-    </row>
-    <row r="28" spans="2:20">
+      <c r="M27" s="111"/>
+    </row>
+    <row r="28" spans="2:19">
       <c r="B28" s="120"/>
-      <c r="C28" s="107" t="s">
+      <c r="C28" s="106" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="3">
         <v>59178</v>
       </c>
       <c r="E28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>12.59</v>
       </c>
-      <c r="F28" s="101">
+      <c r="F28" s="100">
         <v>4600</v>
       </c>
-      <c r="G28" s="101">
+      <c r="G28" s="100">
         <v>4619</v>
       </c>
       <c r="H28">
@@ -13931,17 +13861,18 @@
       <c r="L28">
         <v>4699</v>
       </c>
-    </row>
-    <row r="29" spans="2:20">
+      <c r="M28" s="111"/>
+    </row>
+    <row r="29" spans="2:19">
       <c r="B29" s="120"/>
-      <c r="C29" s="107" t="s">
+      <c r="C29" s="106" t="s">
         <v>42</v>
       </c>
       <c r="D29" s="3">
         <v>49316</v>
       </c>
       <c r="E29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>12.33</v>
       </c>
       <c r="F29">
@@ -13965,63 +13896,65 @@
       <c r="L29">
         <v>3999</v>
       </c>
-    </row>
-    <row r="30" spans="2:20">
+      <c r="M29" s="111"/>
+    </row>
+    <row r="30" spans="2:19">
       <c r="B30" s="120"/>
-      <c r="C30" s="107" t="s">
+      <c r="C30" s="106" t="s">
         <v>48</v>
       </c>
       <c r="D30" s="3">
         <v>44404</v>
       </c>
       <c r="E30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>12.69</v>
       </c>
-      <c r="F30" s="101">
+      <c r="F30" s="100">
         <v>3297</v>
       </c>
-      <c r="G30" s="99">
+      <c r="G30" s="98">
         <v>3249</v>
       </c>
-      <c r="H30" s="99">
+      <c r="H30" s="98">
         <v>3499</v>
       </c>
-      <c r="I30" s="99">
+      <c r="I30" s="98">
         <v>3612</v>
       </c>
       <c r="J30">
         <v>3539</v>
       </c>
-      <c r="K30" s="99">
+      <c r="K30" s="98">
         <v>3399</v>
       </c>
       <c r="L30">
         <v>3499</v>
       </c>
-    </row>
-    <row r="31" spans="2:20">
+      <c r="M30" s="111"/>
+    </row>
+    <row r="31" spans="2:19">
       <c r="B31" s="120"/>
-      <c r="C31" s="107" t="s">
+      <c r="C31" s="106" t="s">
         <v>52</v>
       </c>
       <c r="D31" s="5">
         <v>37268</v>
       </c>
       <c r="E31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>12.86</v>
       </c>
-      <c r="F31" s="99">
+      <c r="F31" s="98">
         <v>2789</v>
       </c>
-      <c r="G31" s="101">
+      <c r="G31" s="100">
         <v>2900</v>
       </c>
-      <c r="H31" s="99">
+      <c r="H31" s="98">
         <v>2799</v>
       </c>
-      <c r="I31" s="101">
+      <c r="I31" s="100">
         <v>2779</v>
       </c>
       <c r="J31">
@@ -14033,55 +13966,59 @@
       <c r="L31">
         <v>2899</v>
       </c>
-    </row>
-    <row r="32" spans="2:20">
+      <c r="M31" s="111"/>
+    </row>
+    <row r="32" spans="2:19">
       <c r="B32" s="120"/>
-      <c r="C32" s="107" t="s">
+      <c r="C32" s="106" t="s">
         <v>74</v>
       </c>
       <c r="D32" s="118">
         <v>23981</v>
       </c>
       <c r="E32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>13.64</v>
       </c>
       <c r="F32" s="4"/>
-      <c r="H32" s="101">
+      <c r="H32" s="100">
         <v>1849</v>
       </c>
-      <c r="I32" s="99">
+      <c r="I32" s="98">
         <v>1785</v>
       </c>
-      <c r="J32" s="99">
+      <c r="J32" s="98">
         <v>1756</v>
       </c>
-      <c r="K32" s="99">
+      <c r="K32" s="98">
         <v>1727</v>
       </c>
-      <c r="L32" s="99">
+      <c r="L32" s="98">
         <v>1758</v>
       </c>
-      <c r="M32">
-        <f t="shared" si="0"/>
-        <v>-135</v>
-      </c>
-      <c r="N32" s="101">
+      <c r="M32" s="1" t="str">
+        <f>TEXT((S32-L32)/L32,"0.0%")</f>
+        <v>36.5%</v>
+      </c>
+      <c r="N32" s="100">
         <v>1623</v>
       </c>
       <c r="O32">
         <v>1739</v>
       </c>
+      <c r="Q32">
+        <v>1874</v>
+      </c>
+      <c r="R32">
+        <v>2000</v>
+      </c>
       <c r="S32">
-        <v>1874</v>
-      </c>
-      <c r="T32">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19">
       <c r="B33" s="120"/>
-      <c r="C33" s="107">
+      <c r="C33" s="106">
         <v>7600</v>
       </c>
       <c r="D33" s="118">
@@ -14090,7 +14027,7 @@
       <c r="F33">
         <v>1699</v>
       </c>
-      <c r="G33" s="101">
+      <c r="G33" s="100">
         <v>1748</v>
       </c>
       <c r="H33">
@@ -14099,19 +14036,19 @@
       <c r="I33">
         <v>2099</v>
       </c>
-      <c r="J33" s="101">
+      <c r="J33" s="100">
         <v>1700</v>
       </c>
-      <c r="K33" s="101">
+      <c r="K33" s="100">
         <v>1688</v>
       </c>
     </row>
-    <row r="34" spans="2:20">
+    <row r="34" spans="2:19">
       <c r="B34" s="121" t="s">
-        <v>343</v>
-      </c>
-      <c r="C34" s="107" t="s">
-        <v>344</v>
+        <v>341</v>
+      </c>
+      <c r="C34" s="106" t="s">
+        <v>342</v>
       </c>
       <c r="D34" s="118">
         <v>27231</v>
@@ -14129,25 +14066,25 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="35" spans="2:20">
+    <row r="35" spans="2:19">
       <c r="B35" s="122"/>
-      <c r="C35" s="107" t="s">
+      <c r="C35" s="106" t="s">
         <v>76</v>
       </c>
       <c r="D35" s="118">
         <v>23560</v>
       </c>
       <c r="E35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>11.85</v>
       </c>
-      <c r="F35" s="99">
+      <c r="F35" s="98">
         <v>1699</v>
       </c>
       <c r="G35">
         <v>1909</v>
       </c>
-      <c r="H35" s="99">
+      <c r="H35" s="98">
         <v>1889</v>
       </c>
       <c r="I35">
@@ -14163,9 +14100,9 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="36" spans="2:20">
+    <row r="36" spans="2:19">
       <c r="B36" s="122"/>
-      <c r="C36" s="107" t="s">
+      <c r="C36" s="106" t="s">
         <v>80</v>
       </c>
       <c r="D36" s="118">
@@ -14178,9 +14115,9 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="37" spans="2:20">
+    <row r="37" spans="2:19">
       <c r="B37" s="122"/>
-      <c r="C37" s="107">
+      <c r="C37" s="106">
         <v>6600</v>
       </c>
       <c r="D37" s="123">
@@ -14202,9 +14139,9 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="38" spans="2:20">
+    <row r="38" spans="2:19">
       <c r="B38" s="122"/>
-      <c r="C38" s="107" t="s">
+      <c r="C38" s="106" t="s">
         <v>95</v>
       </c>
       <c r="D38" s="124">
@@ -14226,9 +14163,9 @@
         <v>888</v>
       </c>
     </row>
-    <row r="39" spans="2:20">
+    <row r="39" spans="2:19">
       <c r="B39" s="122"/>
-      <c r="C39" s="107">
+      <c r="C39" s="106">
         <v>6400</v>
       </c>
       <c r="D39" s="124">
@@ -14250,18 +14187,18 @@
         <v>949</v>
       </c>
     </row>
-    <row r="40" spans="2:20">
+    <row r="40" spans="2:19">
       <c r="B40" s="125" t="s">
-        <v>345</v>
-      </c>
-      <c r="C40" s="107" t="s">
+        <v>343</v>
+      </c>
+      <c r="C40" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D40" s="5">
         <v>32989</v>
       </c>
       <c r="E40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>18.04</v>
       </c>
       <c r="F40" s="88">
@@ -14285,31 +14222,38 @@
       <c r="L40" s="88">
         <v>1829</v>
       </c>
+      <c r="M40" s="1" t="str">
+        <f>TEXT((S40-L40)/L40,"0.0%")</f>
+        <v>47.6%</v>
+      </c>
       <c r="N40">
         <v>1899</v>
       </c>
       <c r="O40">
         <v>1848</v>
       </c>
-      <c r="R40" s="89">
+      <c r="P40" s="89">
         <v>1839</v>
       </c>
+      <c r="Q40">
+        <v>2099</v>
+      </c>
+      <c r="R40">
+        <v>2400</v>
+      </c>
       <c r="S40">
-        <v>2099</v>
-      </c>
-      <c r="T40">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="41" spans="2:20">
-      <c r="C41" s="107" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19">
+      <c r="C41" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="R41">
+      <c r="P41">
         <v>1479</v>
       </c>
     </row>
-    <row r="42" spans="2:20">
+    <row r="42" spans="2:19">
       <c r="F42">
         <v>15</v>
       </c>
@@ -14406,7 +14350,7 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="87" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B2" t="s">
         <v>123</v>
@@ -14628,13 +14572,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="90" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B9" s="91" t="s">
         <v>129</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D9">
         <v>3850</v>
@@ -14661,7 +14605,7 @@
         <v>131</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D10" s="89">
         <v>2749</v>
@@ -14691,7 +14635,7 @@
       <c r="L10" s="89">
         <v>2490</v>
       </c>
-      <c r="O10" s="93">
+      <c r="O10" s="4">
         <v>2470</v>
       </c>
     </row>
@@ -14701,7 +14645,7 @@
         <v>136</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D11" s="88">
         <v>2105</v>
@@ -14741,7 +14685,7 @@
         <v>148</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D12" s="88">
         <v>1152</v>
@@ -14896,14 +14840,14 @@
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="94" t="s">
-        <v>349</v>
+      <c r="A16" s="93" t="s">
+        <v>347</v>
       </c>
       <c r="B16" s="91" t="s">
         <v>127</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D16">
         <v>3599</v>
@@ -14925,12 +14869,12 @@
       <c r="R16" s="4"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="95"/>
+      <c r="A17" s="94"/>
       <c r="B17" t="s">
         <v>132</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D17">
         <v>2895</v>
@@ -14962,12 +14906,12 @@
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="95"/>
+      <c r="A18" s="94"/>
       <c r="B18" t="s">
         <v>140</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D18">
         <v>1966</v>
@@ -14999,12 +14943,12 @@
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="95"/>
+      <c r="A19" s="94"/>
       <c r="B19" s="91" t="s">
         <v>149</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D19">
         <v>1207</v>
@@ -15042,7 +14986,7 @@
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="95"/>
+      <c r="A20" s="94"/>
       <c r="B20" s="91" t="s">
         <v>162</v>
       </c>
@@ -15076,7 +15020,7 @@
       </c>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="95"/>
+      <c r="A21" s="94"/>
       <c r="B21" s="91" t="s">
         <v>167</v>
       </c>
@@ -15116,7 +15060,7 @@
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="95"/>
+      <c r="A22" s="94"/>
       <c r="B22" s="91" t="s">
         <v>178</v>
       </c>
@@ -15156,8 +15100,8 @@
       </c>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="96" t="s">
-        <v>350</v>
+      <c r="A23" s="95" t="s">
+        <v>348</v>
       </c>
       <c r="B23" s="91" t="s">
         <v>144</v>
@@ -15192,7 +15136,7 @@
       </c>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="97"/>
+      <c r="A24" s="96"/>
       <c r="B24" s="91" t="s">
         <v>153</v>
       </c>
@@ -15226,7 +15170,7 @@
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="97"/>
+      <c r="A25" s="96"/>
       <c r="B25" s="91" t="s">
         <v>160</v>
       </c>
@@ -15266,7 +15210,7 @@
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="97"/>
+      <c r="A26" s="96"/>
       <c r="B26" s="91" t="s">
         <v>173</v>
       </c>
@@ -15300,7 +15244,7 @@
       </c>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="97"/>
+      <c r="A27" s="96"/>
       <c r="B27" s="91" t="s">
         <v>176</v>
       </c>
@@ -15340,7 +15284,7 @@
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="97"/>
+      <c r="A28" s="96"/>
       <c r="B28" s="91" t="s">
         <v>179</v>
       </c>
@@ -15380,8 +15324,8 @@
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:15">
-      <c r="A29" s="98" t="s">
-        <v>351</v>
+      <c r="A29" s="97" t="s">
+        <v>349</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>119</v>
@@ -15407,89 +15351,89 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:15">
-      <c r="A30" s="98"/>
+      <c r="A30" s="97"/>
       <c r="B30" t="s">
         <v>121</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="99">
+      <c r="F30" s="98">
         <v>5499</v>
       </c>
-      <c r="G30" s="99">
+      <c r="G30" s="98">
         <v>4789</v>
       </c>
-      <c r="H30" s="99">
+      <c r="H30" s="98">
         <v>4649</v>
       </c>
-      <c r="I30" s="99">
+      <c r="I30" s="98">
         <v>4649</v>
       </c>
-      <c r="J30" s="99">
+      <c r="J30" s="98">
         <v>4679</v>
       </c>
       <c r="K30" s="5">
         <f t="shared" si="0"/>
         <v>-880</v>
       </c>
-      <c r="L30" s="99">
+      <c r="L30" s="98">
         <v>3799</v>
       </c>
-      <c r="M30" s="100">
+      <c r="M30" s="99">
         <v>3888</v>
       </c>
       <c r="N30">
         <v>4127</v>
       </c>
-      <c r="O30" s="101">
+      <c r="O30" s="100">
         <v>3889</v>
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="98"/>
+      <c r="A31" s="97"/>
       <c r="B31" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="99">
+      <c r="D31" s="98">
         <v>3888</v>
       </c>
-      <c r="E31" s="99">
+      <c r="E31" s="98">
         <v>3899</v>
       </c>
-      <c r="F31" s="99">
+      <c r="F31" s="98">
         <v>3798</v>
       </c>
-      <c r="G31" s="99">
+      <c r="G31" s="98">
         <v>3765</v>
       </c>
-      <c r="H31" s="99">
+      <c r="H31" s="98">
         <v>3629</v>
       </c>
-      <c r="I31" s="99">
+      <c r="I31" s="98">
         <v>3629</v>
       </c>
-      <c r="J31" s="99">
+      <c r="J31" s="98">
         <v>3529</v>
       </c>
       <c r="K31" s="5">
         <f t="shared" si="0"/>
         <v>-727</v>
       </c>
-      <c r="L31" s="99">
+      <c r="L31" s="98">
         <v>2802</v>
       </c>
-      <c r="M31" s="99">
+      <c r="M31" s="98">
         <v>2766</v>
       </c>
-      <c r="N31" s="101">
+      <c r="N31" s="100">
         <v>2826</v>
       </c>
-      <c r="O31" s="99">
+      <c r="O31" s="98">
         <v>2778</v>
       </c>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="98"/>
+      <c r="A32" s="97"/>
       <c r="B32" t="s">
         <v>134</v>
       </c>
@@ -15514,7 +15458,7 @@
         <f t="shared" si="0"/>
         <v>-569</v>
       </c>
-      <c r="L32" s="101">
+      <c r="L32" s="100">
         <v>3280</v>
       </c>
       <c r="O32">
@@ -15522,14 +15466,14 @@
       </c>
     </row>
     <row r="33" spans="1:18">
-      <c r="A33" s="98"/>
+      <c r="A33" s="97"/>
       <c r="B33" t="s">
         <v>135</v>
       </c>
-      <c r="D33" s="99">
+      <c r="D33" s="98">
         <v>2688</v>
       </c>
-      <c r="E33" s="99">
+      <c r="E33" s="98">
         <v>2710</v>
       </c>
       <c r="F33">
@@ -15551,15 +15495,15 @@
         <f t="shared" si="0"/>
         <v>-480</v>
       </c>
-      <c r="L33" s="101">
+      <c r="L33" s="100">
         <v>2049</v>
       </c>
-      <c r="O33" s="101">
+      <c r="O33" s="100">
         <v>2179</v>
       </c>
     </row>
     <row r="34" spans="1:18">
-      <c r="A34" s="98"/>
+      <c r="A34" s="97"/>
       <c r="B34" s="16" t="s">
         <v>143</v>
       </c>
@@ -15570,150 +15514,150 @@
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
-      <c r="L34" s="101">
+      <c r="L34" s="100">
         <v>2999</v>
       </c>
-      <c r="M34" s="101">
+      <c r="M34" s="100">
         <v>2848</v>
       </c>
-      <c r="N34" s="99">
+      <c r="N34" s="98">
         <v>2709</v>
       </c>
-      <c r="O34" s="99">
+      <c r="O34" s="98">
         <v>2646</v>
       </c>
     </row>
     <row r="35" spans="1:18">
-      <c r="A35" s="98"/>
+      <c r="A35" s="97"/>
       <c r="B35" t="s">
         <v>146</v>
       </c>
       <c r="D35">
         <v>4398</v>
       </c>
-      <c r="E35" s="99">
+      <c r="E35" s="98">
         <v>4098</v>
       </c>
-      <c r="F35" s="99">
+      <c r="F35" s="98">
         <v>3689</v>
       </c>
-      <c r="G35" s="99">
+      <c r="G35" s="98">
         <v>3599</v>
       </c>
-      <c r="H35" s="99">
+      <c r="H35" s="98">
         <v>3309</v>
       </c>
-      <c r="I35" s="99">
+      <c r="I35" s="98">
         <v>3309</v>
       </c>
-      <c r="J35" s="99">
+      <c r="J35" s="98">
         <v>3139</v>
       </c>
       <c r="K35" s="5">
         <f>L35-J35</f>
         <v>-550</v>
       </c>
-      <c r="L35" s="99">
+      <c r="L35" s="98">
         <v>2589</v>
       </c>
-      <c r="M35" s="99">
+      <c r="M35" s="98">
         <v>2509</v>
       </c>
-      <c r="N35" s="99">
+      <c r="N35" s="98">
         <v>2449</v>
       </c>
-      <c r="O35" s="99">
+      <c r="O35" s="98">
         <v>2389</v>
       </c>
     </row>
     <row r="36" spans="1:18">
-      <c r="A36" s="98"/>
+      <c r="A36" s="97"/>
       <c r="B36" t="s">
         <v>150</v>
       </c>
-      <c r="D36" s="99">
+      <c r="D36" s="98">
         <v>1789</v>
       </c>
-      <c r="E36" s="99">
+      <c r="E36" s="98">
         <v>1889</v>
       </c>
-      <c r="F36" s="99">
+      <c r="F36" s="98">
         <v>1788</v>
       </c>
-      <c r="G36" s="99">
+      <c r="G36" s="98">
         <v>1789</v>
       </c>
-      <c r="H36" s="99">
+      <c r="H36" s="98">
         <v>1839</v>
       </c>
-      <c r="I36" s="99">
+      <c r="I36" s="98">
         <v>1839</v>
       </c>
-      <c r="J36" s="99">
+      <c r="J36" s="98">
         <v>1719</v>
       </c>
       <c r="K36" s="5">
         <f>L36-J36</f>
         <v>-350</v>
       </c>
-      <c r="L36" s="99">
+      <c r="L36" s="98">
         <v>1369</v>
       </c>
-      <c r="M36" s="99">
+      <c r="M36" s="98">
         <v>1358</v>
       </c>
-      <c r="N36" s="99">
+      <c r="N36" s="98">
         <v>1379</v>
       </c>
-      <c r="O36" s="99">
+      <c r="O36" s="98">
         <v>1338</v>
       </c>
     </row>
     <row r="37" spans="1:18">
-      <c r="A37" s="98"/>
+      <c r="A37" s="97"/>
       <c r="B37" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="99">
+      <c r="D37" s="98">
         <v>1258</v>
       </c>
-      <c r="E37" s="99">
+      <c r="E37" s="98">
         <v>1309</v>
       </c>
-      <c r="F37" s="99">
+      <c r="F37" s="98">
         <v>1249</v>
       </c>
-      <c r="G37" s="99">
+      <c r="G37" s="98">
         <v>1133</v>
       </c>
-      <c r="H37" s="99">
+      <c r="H37" s="98">
         <v>1299</v>
       </c>
-      <c r="I37" s="99">
+      <c r="I37" s="98">
         <v>1299</v>
       </c>
-      <c r="J37" s="99">
+      <c r="J37" s="98">
         <v>1280</v>
       </c>
       <c r="K37" s="5">
         <f>L37-J37</f>
         <v>-254</v>
       </c>
-      <c r="L37" s="99">
+      <c r="L37" s="98">
         <v>1026</v>
       </c>
-      <c r="M37" s="99">
+      <c r="M37" s="98">
         <v>1017</v>
       </c>
-      <c r="N37" s="99">
+      <c r="N37" s="98">
         <v>1045</v>
       </c>
-      <c r="O37" s="99">
+      <c r="O37" s="98">
         <v>998</v>
       </c>
     </row>
     <row r="38" spans="1:18">
-      <c r="A38" s="98"/>
+      <c r="A38" s="97"/>
       <c r="B38" s="16" t="s">
         <v>159</v>
       </c>
@@ -15725,27 +15669,27 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
-      <c r="L38" s="99">
+      <c r="L38" s="98">
         <v>909</v>
       </c>
-      <c r="M38" s="99">
+      <c r="M38" s="98">
         <v>877</v>
       </c>
-      <c r="N38" s="99">
+      <c r="N38" s="98">
         <v>839</v>
       </c>
-      <c r="O38" s="99">
+      <c r="O38" s="98">
         <v>826</v>
       </c>
     </row>
     <row r="39" spans="1:18">
-      <c r="A39" s="102" t="s">
-        <v>352</v>
+      <c r="A39" s="101" t="s">
+        <v>350</v>
       </c>
       <c r="B39" t="s">
         <v>125</v>
       </c>
-      <c r="D39" s="99">
+      <c r="D39" s="98">
         <v>3779</v>
       </c>
       <c r="E39">
@@ -15775,26 +15719,26 @@
       </c>
     </row>
     <row r="40" spans="1:18">
-      <c r="A40" s="102"/>
+      <c r="A40" s="101"/>
       <c r="B40" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="99">
+      <c r="D40" s="98">
         <v>2919</v>
       </c>
-      <c r="E40" s="99">
+      <c r="E40" s="98">
         <v>3098</v>
       </c>
       <c r="F40">
         <v>3299</v>
       </c>
-      <c r="G40" s="99">
+      <c r="G40" s="98">
         <v>2899</v>
       </c>
-      <c r="H40" s="101">
+      <c r="H40" s="100">
         <v>2899</v>
       </c>
-      <c r="I40" s="101">
+      <c r="I40" s="100">
         <v>2899</v>
       </c>
       <c r="J40">
@@ -15809,7 +15753,7 @@
       </c>
     </row>
     <row r="41" spans="1:18">
-      <c r="A41" s="102"/>
+      <c r="A41" s="101"/>
       <c r="B41" t="s">
         <v>139</v>
       </c>
@@ -15837,11 +15781,11 @@
       <c r="K41" s="4"/>
     </row>
     <row r="42" spans="1:18">
-      <c r="A42" s="102"/>
+      <c r="A42" s="101"/>
       <c r="B42" t="s">
         <v>138</v>
       </c>
-      <c r="D42" s="99">
+      <c r="D42" s="98">
         <v>2229</v>
       </c>
       <c r="E42">
@@ -15871,50 +15815,50 @@
       </c>
     </row>
     <row r="43" spans="1:18">
-      <c r="A43" s="102"/>
+      <c r="A43" s="101"/>
       <c r="B43" t="s">
         <v>152</v>
       </c>
       <c r="D43">
         <v>3199</v>
       </c>
-      <c r="E43" s="101">
+      <c r="E43" s="100">
         <v>2799</v>
       </c>
-      <c r="F43" s="99">
+      <c r="F43" s="98">
         <v>2428</v>
       </c>
-      <c r="G43" s="99">
+      <c r="G43" s="98">
         <v>2378</v>
       </c>
-      <c r="H43" s="99">
+      <c r="H43" s="98">
         <v>2289</v>
       </c>
-      <c r="I43" s="99">
+      <c r="I43" s="98">
         <v>2289</v>
       </c>
-      <c r="J43" s="99">
+      <c r="J43" s="98">
         <v>2220</v>
       </c>
       <c r="K43" s="5">
         <f>L43-J43</f>
         <v>-561</v>
       </c>
-      <c r="L43" s="99">
+      <c r="L43" s="98">
         <v>1659</v>
       </c>
-      <c r="M43" s="101">
+      <c r="M43" s="100">
         <v>1797</v>
       </c>
-      <c r="N43" s="101">
+      <c r="N43" s="100">
         <v>1737</v>
       </c>
-      <c r="O43" s="99">
+      <c r="O43" s="98">
         <v>1609</v>
       </c>
     </row>
     <row r="44" spans="1:18">
-      <c r="A44" s="102"/>
+      <c r="A44" s="101"/>
       <c r="B44" t="s">
         <v>151</v>
       </c>
@@ -15930,25 +15874,25 @@
       <c r="G44">
         <v>1170</v>
       </c>
-      <c r="H44" s="101">
+      <c r="H44" s="100">
         <v>1189</v>
       </c>
-      <c r="I44" s="101">
+      <c r="I44" s="100">
         <v>1189</v>
       </c>
-      <c r="J44" s="101">
+      <c r="J44" s="100">
         <v>1239</v>
       </c>
       <c r="K44" s="5">
         <f>L44-J44</f>
         <v>-520</v>
       </c>
-      <c r="L44" s="99">
+      <c r="L44" s="98">
         <v>719</v>
       </c>
     </row>
     <row r="45" spans="1:18">
-      <c r="A45" s="102"/>
+      <c r="A45" s="101"/>
       <c r="B45" t="s">
         <v>158</v>
       </c>
@@ -15976,75 +15920,75 @@
       <c r="K45" s="4"/>
     </row>
     <row r="46" spans="1:18">
-      <c r="A46" s="102"/>
+      <c r="A46" s="101"/>
       <c r="B46" t="s">
         <v>164</v>
       </c>
-      <c r="D46" s="99">
+      <c r="D46" s="98">
         <v>903</v>
       </c>
-      <c r="E46" s="99">
+      <c r="E46" s="98">
         <v>955</v>
       </c>
-      <c r="F46" s="99">
+      <c r="F46" s="98">
         <v>895</v>
       </c>
-      <c r="G46" s="99">
+      <c r="G46" s="98">
         <v>883</v>
       </c>
-      <c r="H46" s="99">
+      <c r="H46" s="98">
         <v>890</v>
       </c>
-      <c r="I46" s="99">
+      <c r="I46" s="98">
         <v>890</v>
       </c>
-      <c r="J46" s="99">
+      <c r="J46" s="98">
         <v>849</v>
       </c>
       <c r="K46" s="5">
         <f>L46-J46</f>
         <v>-227</v>
       </c>
-      <c r="L46" s="101">
+      <c r="L46" s="100">
         <v>622</v>
       </c>
-      <c r="M46" s="101">
+      <c r="M46" s="100">
         <v>629</v>
       </c>
-      <c r="N46" s="101">
+      <c r="N46" s="100">
         <v>634</v>
       </c>
-      <c r="O46" s="101">
+      <c r="O46" s="100">
         <v>600</v>
       </c>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="102"/>
+      <c r="A47" s="101"/>
       <c r="B47" t="s">
         <v>168</v>
       </c>
-      <c r="E47" s="99">
+      <c r="E47" s="98">
         <v>819</v>
       </c>
-      <c r="F47" s="99">
+      <c r="F47" s="98">
         <v>706</v>
       </c>
-      <c r="G47" s="99">
+      <c r="G47" s="98">
         <v>811</v>
       </c>
-      <c r="H47" s="99">
+      <c r="H47" s="98">
         <v>790</v>
       </c>
-      <c r="I47" s="99">
+      <c r="I47" s="98">
         <v>790</v>
       </c>
-      <c r="J47" s="99">
+      <c r="J47" s="98">
         <v>765</v>
       </c>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="103" t="s">
-        <v>353</v>
+      <c r="A48" s="102" t="s">
+        <v>351</v>
       </c>
       <c r="B48" s="91" t="s">
         <v>141</v>
@@ -16061,7 +16005,7 @@
       <c r="R48" s="4"/>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="104"/>
+      <c r="A49" s="103"/>
       <c r="B49" s="91" t="s">
         <v>147</v>
       </c>
@@ -16077,17 +16021,17 @@
       <c r="R49" s="4"/>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="104"/>
+      <c r="A50" s="103"/>
       <c r="B50" s="91" t="s">
         <v>165</v>
       </c>
-      <c r="D50" s="101">
+      <c r="D50" s="100">
         <v>1097</v>
       </c>
-      <c r="E50" s="101">
+      <c r="E50" s="100">
         <v>1369</v>
       </c>
-      <c r="F50" s="101">
+      <c r="F50" s="100">
         <v>1449</v>
       </c>
       <c r="G50">
@@ -16104,29 +16048,29 @@
       </c>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="104"/>
+      <c r="A51" s="103"/>
       <c r="B51" s="91" t="s">
         <v>163</v>
       </c>
-      <c r="D51" s="101">
+      <c r="D51" s="100">
         <v>699</v>
       </c>
-      <c r="E51" s="101">
+      <c r="E51" s="100">
         <v>735</v>
       </c>
-      <c r="F51" s="101">
+      <c r="F51" s="100">
         <v>718</v>
       </c>
-      <c r="G51" s="101">
+      <c r="G51" s="100">
         <v>723</v>
       </c>
-      <c r="H51" s="101">
+      <c r="H51" s="100">
         <v>723</v>
       </c>
-      <c r="I51" s="101">
+      <c r="I51" s="100">
         <v>723</v>
       </c>
-      <c r="J51" s="101">
+      <c r="J51" s="100">
         <v>695</v>
       </c>
       <c r="K51" s="1">
@@ -16138,7 +16082,7 @@
       </c>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="104"/>
+      <c r="A52" s="103"/>
       <c r="B52" s="91" t="s">
         <v>170</v>
       </c>
@@ -16149,13 +16093,13 @@
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
-      <c r="H52" s="99">
+      <c r="H52" s="98">
         <v>580</v>
       </c>
-      <c r="I52" s="99">
+      <c r="I52" s="98">
         <v>580</v>
       </c>
-      <c r="J52" s="99">
+      <c r="J52" s="98">
         <v>579</v>
       </c>
       <c r="K52" s="1">
@@ -16167,20 +16111,20 @@
       </c>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="104"/>
+      <c r="A53" s="103"/>
       <c r="B53" s="91" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="99">
+      <c r="D53" s="98">
         <v>539</v>
       </c>
-      <c r="E53" s="99">
+      <c r="E53" s="98">
         <v>548</v>
       </c>
-      <c r="F53" s="99">
+      <c r="F53" s="98">
         <v>528</v>
       </c>
-      <c r="G53" s="99">
+      <c r="G53" s="98">
         <v>539</v>
       </c>
       <c r="H53">
@@ -16189,7 +16133,7 @@
       <c r="I53">
         <v>560</v>
       </c>
-      <c r="J53" s="101">
+      <c r="J53" s="100">
         <v>548</v>
       </c>
       <c r="K53" s="1">
@@ -16207,7 +16151,7 @@
       </c>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="104"/>
+      <c r="A54" s="103"/>
       <c r="B54" s="91" t="s">
         <v>174</v>
       </c>
@@ -16229,7 +16173,7 @@
       </c>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="104"/>
+      <c r="A55" s="103"/>
       <c r="B55" s="91" t="s">
         <v>175</v>
       </c>
@@ -16245,10 +16189,10 @@
       <c r="G55">
         <v>409</v>
       </c>
-      <c r="H55" s="101">
+      <c r="H55" s="100">
         <v>399</v>
       </c>
-      <c r="I55" s="101">
+      <c r="I55" s="100">
         <v>399</v>
       </c>
       <c r="J55">
@@ -16263,43 +16207,43 @@
       </c>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="105" t="s">
+      <c r="A58" s="104" t="s">
+        <v>352</v>
+      </c>
+      <c r="B58" s="104"/>
+      <c r="C58" s="104"/>
+      <c r="D58" s="104"/>
+      <c r="F58" s="105" t="s">
+        <v>353</v>
+      </c>
+      <c r="G58" s="105"/>
+      <c r="H58" s="105"/>
+      <c r="I58" s="105"/>
+      <c r="J58" s="105"/>
+      <c r="K58" s="105"/>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" s="105"/>
+      <c r="B59" s="105"/>
+      <c r="C59" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="B58" s="105"/>
-      <c r="C58" s="105"/>
-      <c r="D58" s="105"/>
-      <c r="F58" s="106" t="s">
+      <c r="D59" t="s">
         <v>355</v>
       </c>
-      <c r="G58" s="106"/>
-      <c r="H58" s="106"/>
-      <c r="I58" s="106"/>
-      <c r="J58" s="106"/>
-      <c r="K58" s="106"/>
-    </row>
-    <row r="59" spans="1:18">
-      <c r="A59" s="106"/>
-      <c r="B59" s="106"/>
-      <c r="C59" s="4" t="s">
+      <c r="F59" s="105"/>
+      <c r="G59" s="105"/>
+      <c r="H59" s="105"/>
+      <c r="I59" s="105"/>
+      <c r="J59" s="105"/>
+      <c r="K59" s="105"/>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" s="105" t="s">
         <v>356</v>
       </c>
-      <c r="D59" t="s">
+      <c r="B60" s="105" t="s">
         <v>357</v>
-      </c>
-      <c r="F59" s="106"/>
-      <c r="G59" s="106"/>
-      <c r="H59" s="106"/>
-      <c r="I59" s="106"/>
-      <c r="J59" s="106"/>
-      <c r="K59" s="106"/>
-    </row>
-    <row r="60" spans="1:18">
-      <c r="A60" s="106" t="s">
-        <v>358</v>
-      </c>
-      <c r="B60" s="106" t="s">
-        <v>359</v>
       </c>
       <c r="C60" s="4">
         <v>24</v>
@@ -16309,9 +16253,9 @@
       </c>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="106"/>
-      <c r="B61" s="106" t="s">
-        <v>360</v>
+      <c r="A61" s="105"/>
+      <c r="B61" s="105" t="s">
+        <v>358</v>
       </c>
       <c r="C61" s="4">
         <v>20</v>
@@ -16321,9 +16265,9 @@
       </c>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="106"/>
-      <c r="B62" s="106" t="s">
-        <v>361</v>
+      <c r="A62" s="105"/>
+      <c r="B62" s="105" t="s">
+        <v>359</v>
       </c>
       <c r="C62" s="4">
         <v>14</v>
@@ -16333,11 +16277,11 @@
       </c>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="106" t="s">
-        <v>362</v>
-      </c>
-      <c r="B63" s="106" t="s">
-        <v>363</v>
+      <c r="A63" s="105" t="s">
+        <v>360</v>
+      </c>
+      <c r="B63" s="105" t="s">
+        <v>361</v>
       </c>
       <c r="C63" s="4">
         <v>24</v>
@@ -16347,9 +16291,9 @@
       </c>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="106"/>
-      <c r="B64" s="106" t="s">
-        <v>364</v>
+      <c r="A64" s="105"/>
+      <c r="B64" s="105" t="s">
+        <v>362</v>
       </c>
       <c r="C64" s="4">
         <v>20</v>
@@ -16359,9 +16303,9 @@
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="106"/>
-      <c r="B65" s="106" t="s">
-        <v>365</v>
+      <c r="A65" s="105"/>
+      <c r="B65" s="105" t="s">
+        <v>363</v>
       </c>
       <c r="C65" s="4">
         <v>14</v>
@@ -16371,9 +16315,9 @@
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="106"/>
-      <c r="B66" s="106" t="s">
-        <v>366</v>
+      <c r="A66" s="105"/>
+      <c r="B66" s="105" t="s">
+        <v>364</v>
       </c>
       <c r="C66" s="4">
         <v>6</v>
@@ -16383,9 +16327,9 @@
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="106"/>
-      <c r="B67" s="106" t="s">
-        <v>367</v>
+      <c r="A67" s="105"/>
+      <c r="B67" s="105" t="s">
+        <v>365</v>
       </c>
       <c r="C67" s="4">
         <v>10</v>
@@ -16395,9 +16339,9 @@
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="106"/>
-      <c r="B68" s="106" t="s">
-        <v>368</v>
+      <c r="A68" s="105"/>
+      <c r="B68" s="105" t="s">
+        <v>366</v>
       </c>
       <c r="C68" s="4">
         <v>4</v>
@@ -16407,11 +16351,11 @@
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="106" t="s">
-        <v>369</v>
-      </c>
-      <c r="B69" s="106" t="s">
-        <v>370</v>
+      <c r="A69" s="105" t="s">
+        <v>367</v>
+      </c>
+      <c r="B69" s="105" t="s">
+        <v>368</v>
       </c>
       <c r="C69" s="4">
         <v>16</v>
@@ -16421,9 +16365,9 @@
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="106"/>
-      <c r="B70" s="106" t="s">
-        <v>363</v>
+      <c r="A70" s="105"/>
+      <c r="B70" s="105" t="s">
+        <v>361</v>
       </c>
       <c r="C70" s="4">
         <v>12</v>
@@ -16433,9 +16377,9 @@
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="106"/>
-      <c r="B71" s="106" t="s">
-        <v>371</v>
+      <c r="A71" s="105"/>
+      <c r="B71" s="105" t="s">
+        <v>369</v>
       </c>
       <c r="C71" s="4">
         <v>8</v>
@@ -16445,9 +16389,9 @@
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="106"/>
-      <c r="B72" s="106" t="s">
-        <v>364</v>
+      <c r="A72" s="105"/>
+      <c r="B72" s="105" t="s">
+        <v>362</v>
       </c>
       <c r="C72" s="4">
         <v>8</v>
@@ -16457,9 +16401,9 @@
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="106"/>
-      <c r="B73" s="106" t="s">
-        <v>365</v>
+      <c r="A73" s="105"/>
+      <c r="B73" s="105" t="s">
+        <v>363</v>
       </c>
       <c r="C73" s="4">
         <v>6</v>
@@ -16469,9 +16413,9 @@
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="106"/>
-      <c r="B74" s="106" t="s">
-        <v>372</v>
+      <c r="A74" s="105"/>
+      <c r="B74" s="105" t="s">
+        <v>370</v>
       </c>
       <c r="C74" s="4">
         <v>6</v>
@@ -16516,19 +16460,19 @@
   <sheetData>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="D2" s="22" t="s">
         <v>374</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="E2" s="23" t="s">
         <v>375</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>376</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>377</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>157</v>
@@ -16537,145 +16481,145 @@
         <v>133</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" ht="33" customHeight="1" spans="1:9">
       <c r="B3" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="D3" s="30" t="s">
         <v>380</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="E3" s="30" t="s">
         <v>381</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="F3" s="30" t="s">
         <v>382</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="G3" s="30" t="s">
         <v>383</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="H3" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="I3" s="30" t="s">
         <v>385</v>
-      </c>
-      <c r="H3" s="30" t="s">
-        <v>386</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1" spans="1:9">
       <c r="B4" s="31"/>
       <c r="C4" s="29" t="s">
+        <v>386</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="E4" s="30" t="s">
         <v>388</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="F4" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="G4" s="30" t="s">
         <v>390</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="H4" s="30" t="s">
         <v>391</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="I4" s="30" t="s">
         <v>392</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>393</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="31"/>
       <c r="C5" s="32" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D5" s="33"/>
       <c r="E5" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>395</v>
+      </c>
+      <c r="G5" s="30" t="s">
         <v>396</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>397</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>398</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="30" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" ht="19.2" spans="1:9">
       <c r="B6" s="31"/>
       <c r="C6" s="34" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E6" s="30" t="s">
         <v>325</v>
       </c>
       <c r="F6" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>401</v>
+      </c>
+      <c r="H6" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="I6" s="30" t="s">
         <v>403</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>404</v>
-      </c>
-      <c r="I6" s="30" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="7" ht="19.2" spans="1:9">
       <c r="B7" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>405</v>
+      </c>
+      <c r="D7" s="30" t="s">
         <v>406</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="E7" s="30" t="s">
         <v>407</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="F7" s="30" t="s">
         <v>408</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="G7" s="30" t="s">
         <v>409</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="H7" s="30" t="s">
         <v>410</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="I7" s="30" t="s">
         <v>411</v>
-      </c>
-      <c r="H7" s="30" t="s">
-        <v>412</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="37"/>
       <c r="C8" s="38" t="s">
+        <v>412</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="E8" s="30" t="s">
         <v>414</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="F8" s="30" t="s">
         <v>415</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>416</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>417</v>
       </c>
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
@@ -16683,107 +16627,107 @@
     </row>
     <row r="9" ht="21" customHeight="1" spans="1:9">
       <c r="B9" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>417</v>
+      </c>
+      <c r="D9" s="30" t="s">
         <v>418</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="E9" s="30" t="s">
         <v>419</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="F9" s="30" t="s">
         <v>420</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="G9" s="30" t="s">
         <v>421</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="H9" s="30" t="s">
         <v>422</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="H9" s="30" t="s">
-        <v>424</v>
       </c>
       <c r="I9" s="33"/>
     </row>
     <row r="10" ht="19.2" spans="1:9">
       <c r="B10" s="41"/>
       <c r="C10" s="40" t="s">
+        <v>423</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="E10" s="30" t="s">
         <v>425</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="F10" s="30" t="s">
         <v>426</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="G10" s="30" t="s">
         <v>427</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="H10" s="30" t="s">
         <v>428</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>429</v>
-      </c>
-      <c r="H10" s="30" t="s">
-        <v>430</v>
       </c>
       <c r="I10" s="33"/>
     </row>
     <row r="11" spans="1:9">
       <c r="B11" s="41"/>
       <c r="C11" s="42" t="s">
+        <v>429</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>430</v>
+      </c>
+      <c r="E11" s="30" t="s">
         <v>431</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="F11" s="30" t="s">
         <v>432</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="G11" s="30" t="s">
         <v>433</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="H11" s="30" t="s">
         <v>434</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>435</v>
-      </c>
-      <c r="H11" s="30" t="s">
-        <v>436</v>
       </c>
       <c r="I11" s="33"/>
     </row>
     <row r="12" spans="1:9">
       <c r="B12" s="41"/>
       <c r="C12" s="43" t="s">
+        <v>435</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="E12" s="30" t="s">
         <v>437</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="F12" s="30" t="s">
         <v>438</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="G12" s="44" t="s">
         <v>439</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="H12" s="44" t="s">
         <v>440</v>
-      </c>
-      <c r="G12" s="44" t="s">
-        <v>441</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>442</v>
       </c>
       <c r="I12" s="33"/>
     </row>
     <row r="13" ht="19.2" spans="1:9">
       <c r="B13" s="41"/>
       <c r="C13" s="45" t="s">
+        <v>441</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="E13" s="30" t="s">
         <v>443</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="F13" s="30" t="s">
         <v>444</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>445</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>446</v>
       </c>
       <c r="G13" s="33"/>
       <c r="H13" s="33"/>
@@ -16792,41 +16736,41 @@
     <row r="14" ht="28.8" spans="1:9">
       <c r="B14" s="41"/>
       <c r="C14" s="46" t="s">
+        <v>445</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>446</v>
+      </c>
+      <c r="E14" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="F14" s="30" t="s">
         <v>448</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="G14" s="30" t="s">
         <v>449</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>450</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>451</v>
       </c>
       <c r="H14" s="33"/>
       <c r="I14" s="33"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:9">
       <c r="B15" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>451</v>
+      </c>
+      <c r="D15" s="30" t="s">
         <v>452</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="E15" s="30" t="s">
         <v>453</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="F15" s="30" t="s">
         <v>454</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="G15" s="44" t="s">
         <v>455</v>
-      </c>
-      <c r="F15" s="30" t="s">
-        <v>456</v>
-      </c>
-      <c r="G15" s="44" t="s">
-        <v>457</v>
       </c>
       <c r="H15" s="33"/>
       <c r="I15" s="33"/>
@@ -16834,13 +16778,13 @@
     <row r="16" ht="19.2" spans="1:9">
       <c r="B16" s="49"/>
       <c r="C16" s="50" t="s">
+        <v>456</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="E16" s="30" t="s">
         <v>458</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>459</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>460</v>
       </c>
       <c r="F16" s="33"/>
       <c r="G16" s="33"/>
@@ -16850,13 +16794,13 @@
     <row r="17" spans="1:9">
       <c r="B17" s="49"/>
       <c r="C17" s="51" t="s">
+        <v>459</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>460</v>
+      </c>
+      <c r="E17" s="30" t="s">
         <v>461</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>462</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>463</v>
       </c>
       <c r="F17" s="33"/>
       <c r="G17" s="33"/>
@@ -16866,14 +16810,14 @@
     <row r="18" spans="1:9">
       <c r="B18" s="49"/>
       <c r="C18" s="52" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="30" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G18" s="33"/>
       <c r="H18" s="33"/>
@@ -16881,19 +16825,19 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
+        <v>465</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>372</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>466</v>
+      </c>
+      <c r="D20" s="55" t="s">
         <v>467</v>
       </c>
-      <c r="B20" s="53" t="s">
-        <v>374</v>
-      </c>
-      <c r="C20" s="54" t="s">
-        <v>468</v>
-      </c>
-      <c r="D20" s="55" t="s">
-        <v>469</v>
-      </c>
       <c r="E20" s="56" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F20" s="57" t="s">
         <v>157</v>
@@ -16902,48 +16846,48 @@
         <v>133</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="I20" s="60" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="B21" s="61" t="s">
+        <v>378</v>
+      </c>
+      <c r="C21" s="62" t="s">
+        <v>468</v>
+      </c>
+      <c r="D21" s="63" t="s">
         <v>380</v>
       </c>
-      <c r="C21" s="62" t="s">
-        <v>470</v>
-      </c>
-      <c r="D21" s="63" t="s">
-        <v>382</v>
-      </c>
       <c r="E21" s="63" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F21" s="64"/>
       <c r="G21" s="63" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H21" s="63" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="I21" s="64"/>
     </row>
     <row r="22" spans="1:9">
       <c r="B22" s="65"/>
       <c r="C22" s="66" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E22" s="63" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F22" s="64"/>
       <c r="G22" s="63" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H22" s="64"/>
       <c r="I22" s="64"/>
@@ -16951,39 +16895,39 @@
     <row r="23" ht="21.6" spans="1:9">
       <c r="B23" s="65"/>
       <c r="C23" s="67" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D23" s="64"/>
       <c r="E23" s="63" t="s">
+        <v>474</v>
+      </c>
+      <c r="F23" s="63" t="s">
+        <v>475</v>
+      </c>
+      <c r="G23" s="63" t="s">
         <v>476</v>
       </c>
-      <c r="F23" s="63" t="s">
+      <c r="H23" s="63" t="s">
         <v>477</v>
       </c>
-      <c r="G23" s="63" t="s">
+      <c r="I23" s="63" t="s">
         <v>478</v>
-      </c>
-      <c r="H23" s="63" t="s">
-        <v>479</v>
-      </c>
-      <c r="I23" s="63" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="B24" s="65"/>
       <c r="C24" s="68" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D24" s="64"/>
       <c r="E24" s="63" t="s">
+        <v>480</v>
+      </c>
+      <c r="F24" s="63" t="s">
+        <v>481</v>
+      </c>
+      <c r="G24" s="63" t="s">
         <v>482</v>
-      </c>
-      <c r="F24" s="63" t="s">
-        <v>483</v>
-      </c>
-      <c r="G24" s="63" t="s">
-        <v>484</v>
       </c>
       <c r="H24" s="64"/>
       <c r="I24" s="64"/>
@@ -16991,81 +16935,81 @@
     <row r="25" spans="1:9">
       <c r="B25" s="65"/>
       <c r="C25" s="69" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D25" s="64"/>
       <c r="E25" s="63" t="s">
+        <v>484</v>
+      </c>
+      <c r="F25" s="63" t="s">
+        <v>485</v>
+      </c>
+      <c r="G25" s="63" t="s">
         <v>486</v>
       </c>
-      <c r="F25" s="63" t="s">
+      <c r="H25" s="63" t="s">
         <v>487</v>
-      </c>
-      <c r="G25" s="63" t="s">
-        <v>488</v>
-      </c>
-      <c r="H25" s="63" t="s">
-        <v>489</v>
       </c>
       <c r="I25" s="64"/>
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="65"/>
       <c r="C26" s="70" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D26" s="64"/>
       <c r="E26" s="63" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F26" s="64"/>
       <c r="G26" s="63" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H26" s="63" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="I26" s="64"/>
     </row>
     <row r="27" ht="21.6" spans="1:9">
       <c r="B27" s="71" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C27" s="72" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D27" s="64"/>
       <c r="E27" s="63" t="s">
+        <v>492</v>
+      </c>
+      <c r="F27" s="63" t="s">
+        <v>493</v>
+      </c>
+      <c r="G27" s="63" t="s">
         <v>494</v>
       </c>
-      <c r="F27" s="63" t="s">
+      <c r="H27" s="63" t="s">
         <v>495</v>
-      </c>
-      <c r="G27" s="63" t="s">
-        <v>496</v>
-      </c>
-      <c r="H27" s="63" t="s">
-        <v>497</v>
       </c>
       <c r="I27" s="64"/>
     </row>
     <row r="28" ht="21.6" spans="1:9">
       <c r="B28" s="73" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C28" s="74" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E28" s="63" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F28" s="63" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G28" s="63" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H28" s="64"/>
       <c r="I28" s="64"/>
@@ -17073,19 +17017,19 @@
     <row r="29" spans="1:9">
       <c r="B29" s="75"/>
       <c r="C29" s="76" t="s">
+        <v>498</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>499</v>
+      </c>
+      <c r="E29" s="63" t="s">
         <v>500</v>
       </c>
-      <c r="D29" s="63" t="s">
+      <c r="F29" s="63" t="s">
         <v>501</v>
       </c>
-      <c r="E29" s="63" t="s">
+      <c r="G29" s="63" t="s">
         <v>502</v>
-      </c>
-      <c r="F29" s="63" t="s">
-        <v>503</v>
-      </c>
-      <c r="G29" s="63" t="s">
-        <v>504</v>
       </c>
       <c r="H29" s="64"/>
       <c r="I29" s="64"/>
@@ -17093,14 +17037,14 @@
     <row r="30" spans="1:9">
       <c r="B30" s="75"/>
       <c r="C30" s="77" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D30" s="64"/>
       <c r="E30" s="63" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F30" s="63" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G30" s="64"/>
       <c r="H30" s="64"/>
@@ -17108,14 +17052,14 @@
     </row>
     <row r="32" ht="15.6" spans="1:9">
       <c r="A32" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B32" s="78"/>
       <c r="C32" s="79" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D32" s="80" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E32" s="81"/>
       <c r="F32" s="82"/>
@@ -17123,64 +17067,64 @@
     <row r="33" ht="15.6" spans="2:6">
       <c r="B33" s="78"/>
       <c r="C33" s="83" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D33" s="80" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E33" s="82"/>
       <c r="F33" s="84" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="34" ht="15.6" spans="2:6">
       <c r="B34" s="78"/>
       <c r="C34" s="83" t="s">
+        <v>510</v>
+      </c>
+      <c r="D34" s="84" t="s">
+        <v>511</v>
+      </c>
+      <c r="E34" s="84" t="s">
         <v>512</v>
       </c>
-      <c r="D34" s="84" t="s">
+      <c r="F34" s="84" t="s">
         <v>513</v>
-      </c>
-      <c r="E34" s="84" t="s">
-        <v>514</v>
-      </c>
-      <c r="F34" s="84" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="35" ht="15.6" spans="2:6">
       <c r="B35" s="78"/>
       <c r="C35" s="85" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D35" s="86"/>
       <c r="E35" s="80" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F35" s="82"/>
     </row>
     <row r="36" ht="15.6" spans="2:6">
       <c r="B36" s="78"/>
       <c r="C36" s="83" t="s">
+        <v>516</v>
+      </c>
+      <c r="D36" s="84" t="s">
+        <v>517</v>
+      </c>
+      <c r="E36" s="84" t="s">
         <v>518</v>
       </c>
-      <c r="D36" s="84" t="s">
+      <c r="F36" s="84" t="s">
         <v>519</v>
-      </c>
-      <c r="E36" s="84" t="s">
-        <v>520</v>
-      </c>
-      <c r="F36" s="84" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="2:6">
       <c r="B37" s="78"/>
       <c r="C37" s="83" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D37" s="84" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E37" s="86"/>
       <c r="F37" s="86"/>
@@ -17245,15 +17189,15 @@
     </row>
     <row r="3" spans="2:11">
       <c r="C3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4" spans="2:11">
       <c r="B4" s="11" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D4">
         <v>11.25</v>
@@ -17274,7 +17218,7 @@
     <row r="5" spans="2:11">
       <c r="B5" s="11"/>
       <c r="C5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D5">
         <v>8.125</v>
@@ -17295,7 +17239,7 @@
     <row r="6" spans="2:11">
       <c r="B6" s="11"/>
       <c r="C6" s="12" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D6" s="12">
         <f t="shared" ref="D6:I6" si="0">ROUND(AVERAGE(D4:D5),2)</f>
@@ -17323,10 +17267,10 @@
     </row>
     <row r="7" spans="2:11">
       <c r="B7" s="13" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D7">
         <f>480/32</f>
@@ -17348,7 +17292,7 @@
     <row r="8" spans="2:11">
       <c r="B8" s="13"/>
       <c r="C8" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D8">
         <f>840/48</f>
@@ -17370,7 +17314,7 @@
     <row r="9" spans="2:11">
       <c r="B9" s="13"/>
       <c r="C9" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D9">
         <f>1100/64</f>
@@ -17392,7 +17336,7 @@
     <row r="10" spans="2:11">
       <c r="B10" s="13"/>
       <c r="C10" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D10">
         <f>1800/96</f>
@@ -17414,13 +17358,13 @@
     <row r="11" spans="2:11">
       <c r="B11" s="13"/>
       <c r="C11" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="2:11">
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D12" s="14">
         <f>ROUND(MAX(D7:D10),2)</f>
@@ -17446,7 +17390,7 @@
     <row r="13" spans="2:11">
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D13" s="14">
         <f>ROUND(MIN(D7:D10),2)</f>
@@ -17471,10 +17415,10 @@
     </row>
     <row r="14" spans="2:11">
       <c r="B14" s="15" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C14" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D14">
         <f>380/1000</f>
@@ -17497,7 +17441,7 @@
     <row r="15" spans="2:11">
       <c r="B15" s="15"/>
       <c r="C15" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D15">
         <v>0.36</v>
@@ -17519,7 +17463,7 @@
     <row r="16" spans="2:11">
       <c r="B16" s="15"/>
       <c r="C16" s="16" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D16" s="16">
         <f>ROUND(AVERAGE(D14:D15),2)</f>
@@ -17544,10 +17488,10 @@
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="17" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C17" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E17">
         <v>1.005</v>
@@ -17565,7 +17509,7 @@
     <row r="18" spans="2:8">
       <c r="B18" s="17"/>
       <c r="C18" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E18">
         <v>0.81</v>
@@ -17584,7 +17528,7 @@
     <row r="19" spans="2:8">
       <c r="B19" s="17"/>
       <c r="C19" s="18" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="18">
@@ -17606,10 +17550,10 @@
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="19" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C20" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E20">
         <v>0.27</v>
@@ -17621,7 +17565,7 @@
     <row r="21" spans="2:8">
       <c r="B21" s="19"/>
       <c r="C21" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E21">
         <v>0.19</v>
@@ -17633,7 +17577,7 @@
     <row r="22" spans="2:8">
       <c r="B22" s="19"/>
       <c r="C22" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E22">
         <v>0.16</v>
@@ -17645,7 +17589,7 @@
     <row r="23" spans="2:8">
       <c r="B23" s="19"/>
       <c r="C23" s="20" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D23" s="20">
         <v>0.15</v>
@@ -17661,18 +17605,18 @@
     </row>
     <row r="27" spans="2:8">
       <c r="B27" t="s">
+        <v>539</v>
+      </c>
+      <c r="C27" t="s">
+        <v>540</v>
+      </c>
+      <c r="D27" t="s">
         <v>541</v>
-      </c>
-      <c r="C27" t="s">
-        <v>542</v>
-      </c>
-      <c r="D27" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="28" spans="2:8">
       <c r="C28" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>
@@ -17686,7 +17630,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B1:K15 B16:F16 I16:K19 B17:G18 B19:F19 B20:K28" formulaRange="1"/>
+    <ignoredError sqref="B20:K28 B19:F19 B17:G18 I16:K19 B16:F16 B1:K15" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17702,13 +17646,13 @@
   <sheetData>
     <row r="4" spans="2:19">
       <c r="C4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D4">
         <v>750</v>
       </c>
       <c r="E4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F4">
         <v>359</v>
@@ -17716,13 +17660,13 @@
     </row>
     <row r="5" spans="2:19">
       <c r="C5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D5">
         <v>850</v>
       </c>
       <c r="E5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F5">
         <v>502</v>
@@ -17730,13 +17674,13 @@
     </row>
     <row r="6" spans="2:19">
       <c r="C6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D6">
         <v>1000</v>
       </c>
       <c r="E6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F6">
         <v>1099</v>
@@ -17744,10 +17688,10 @@
     </row>
     <row r="10" spans="2:19">
       <c r="B10" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C10" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F10">
         <v>528</v>
@@ -17755,7 +17699,7 @@
     </row>
     <row r="11" spans="2:19">
       <c r="C11" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F11">
         <v>449</v>
@@ -17763,77 +17707,77 @@
     </row>
     <row r="13" spans="2:19">
       <c r="B13" t="s">
+        <v>550</v>
+      </c>
+      <c r="C13" t="s">
+        <v>551</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="F13" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="14" spans="2:19">
       <c r="C14" t="s">
+        <v>555</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="H14" t="s">
         <v>560</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="I14" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>562</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="K14" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="J14" t="s">
+      <c r="L14" t="s">
         <v>564</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="M14" t="s">
         <v>565</v>
       </c>
-      <c r="L14" t="s">
+      <c r="N14" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="M14" t="s">
+      <c r="O14" t="s">
         <v>567</v>
       </c>
-      <c r="N14" s="5" t="s">
+      <c r="P14" t="s">
         <v>568</v>
       </c>
-      <c r="O14" t="s">
+      <c r="Q14" t="s">
         <v>569</v>
       </c>
-      <c r="P14" t="s">
+      <c r="R14" t="s">
         <v>570</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="S14" s="5" t="s">
         <v>571</v>
-      </c>
-      <c r="R14" t="s">
-        <v>572</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="15" spans="2:19">
       <c r="D15" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E15" s="5"/>
       <c r="G15" s="5"/>
@@ -17844,60 +17788,60 @@
     </row>
     <row r="16" spans="2:19">
       <c r="C16" t="s">
+        <v>573</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" t="s">
         <v>577</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="I16" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="K16" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="L16" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="N16" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="O16" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="N16" s="5" t="s">
+      <c r="P16" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="Q16" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="P16" s="5" t="s">
+      <c r="R16" t="s">
         <v>587</v>
       </c>
-      <c r="Q16" s="5" t="s">
+      <c r="S16" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="R16" t="s">
-        <v>589</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="17" spans="3:19">
       <c r="C17" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D17" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="18" spans="3:19">
@@ -17934,10 +17878,10 @@
     </row>
     <row r="19" spans="3:19">
       <c r="C19" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D19" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F19" s="2"/>
       <c r="H19" s="3"/>
@@ -17948,7 +17892,7 @@
     </row>
     <row r="20" spans="3:19">
       <c r="D20" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -17958,7 +17902,7 @@
     </row>
     <row r="21" spans="3:19">
       <c r="C21" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D21" t="s">
         <v>274</v>
@@ -17973,7 +17917,7 @@
     </row>
     <row r="22" ht="15.15" spans="3:19">
       <c r="D22" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E22" s="3"/>
       <c r="I22" s="3"/>
@@ -17985,7 +17929,7 @@
     </row>
     <row r="23" spans="3:19">
       <c r="C23" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F23" s="6"/>
       <c r="J23" s="6"/>
@@ -17998,7 +17942,7 @@
     </row>
     <row r="24" ht="15.15" spans="3:19">
       <c r="C24" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
@@ -18018,7 +17962,7 @@
     </row>
     <row r="25" spans="3:19">
       <c r="D25" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="I25" s="5"/>
       <c r="N25" s="5"/>
@@ -18027,19 +17971,19 @@
     </row>
     <row r="26" spans="3:19">
       <c r="D26" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F26" s="3"/>
       <c r="I26" s="3"/>
       <c r="K26" s="2"/>
       <c r="R26" s="3"/>
       <c r="S26" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="27" spans="3:19">
       <c r="D27" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H27" s="3"/>
       <c r="J27" s="3"/>
@@ -18052,47 +17996,47 @@
     </row>
     <row r="28" spans="3:19">
       <c r="C28" t="s">
+        <v>602</v>
+      </c>
+      <c r="D28" t="s">
+        <v>603</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="D28" t="s">
+      <c r="J28" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="O28" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>607</v>
-      </c>
       <c r="P28" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="29" spans="3:19">
       <c r="D29" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="3:19">
       <c r="C30" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D30" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H30" s="3"/>
       <c r="J30" s="3"/>
@@ -18102,7 +18046,7 @@
     </row>
     <row r="31" spans="3:19">
       <c r="D31" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -18110,10 +18054,10 @@
     </row>
     <row r="32" spans="3:19">
       <c r="C32" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D32" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="K32" s="3"/>
       <c r="M32" s="2"/>
@@ -18121,7 +18065,7 @@
     </row>
     <row r="36" spans="3:3">
       <c r="C36" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
